--- a/MDB.xlsx
+++ b/MDB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D6A28F-BD95-43C3-A369-1649DABC9DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41A1735-D2B9-484F-B635-DC603A79CD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21780" yWindow="830" windowWidth="16650" windowHeight="18460" xr2:uid="{9A102858-C73E-5D48-A2CD-E1A822063168}"/>
+    <workbookView xWindow="3870" yWindow="105" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{9A102858-C73E-5D48-A2CD-E1A822063168}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="116">
   <si>
     <t>Price</t>
   </si>
@@ -364,16 +364,65 @@
   </si>
   <si>
     <t>Net Cash</t>
+  </si>
+  <si>
+    <t>Terminal</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Share Price</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>FY27</t>
+  </si>
+  <si>
+    <t>FY28</t>
+  </si>
+  <si>
+    <t>FY29</t>
+  </si>
+  <si>
+    <t>FY30</t>
+  </si>
+  <si>
+    <t>FY31</t>
+  </si>
+  <si>
+    <t>FY32</t>
+  </si>
+  <si>
+    <t>FY33</t>
+  </si>
+  <si>
+    <t>FY34</t>
+  </si>
+  <si>
+    <t>Revenue NPV</t>
+  </si>
+  <si>
+    <t>Revenue NPV assumes all revenue as FCF which is rarely true. Output of this formula should be treated as an upper bound</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -422,10 +471,17 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -445,11 +501,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -477,8 +534,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -487,10 +544,20 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -947,12 +1014,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21F4C51-D0DF-104C-A19C-F0B422EB0491}">
   <dimension ref="B2:L15"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="11" style="14"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B2" s="14" t="s">
         <v>41</v>
       </c>
@@ -960,10 +1027,10 @@
         <v>0</v>
       </c>
       <c r="J2" s="15">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+        <v>316.45999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3" s="14" t="s">
         <v>42</v>
       </c>
@@ -974,22 +1041,20 @@
         <v>1</v>
       </c>
       <c r="J3" s="16">
-        <v>74</v>
-      </c>
-      <c r="K3" s="20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+        <v>81.36</v>
+      </c>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I4" s="14" t="s">
         <v>2</v>
       </c>
       <c r="J4" s="16">
         <f>+J2*J3</f>
-        <v>23680</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+        <v>25747.185599999997</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="14" t="s">
         <v>67</v>
       </c>
@@ -999,11 +1064,9 @@
       <c r="J5" s="16">
         <v>2302</v>
       </c>
-      <c r="K5" s="20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K5" s="20"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="14" t="s">
         <v>70</v>
       </c>
@@ -1013,23 +1076,21 @@
       <c r="J6" s="16">
         <v>1125</v>
       </c>
-      <c r="K6" s="20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K6" s="20"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I7" s="14" t="s">
         <v>5</v>
       </c>
       <c r="J7" s="16">
         <f>+J4-J5+J6</f>
-        <v>22503</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+        <v>24570.185599999997</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L8" s="15"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="14" t="s">
         <v>69</v>
       </c>
@@ -1037,17 +1098,17 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I11" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I12" s="14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B15" s="14" t="s">
         <v>71</v>
       </c>
@@ -1059,25 +1120,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081C1C2F-51E4-5443-871E-C009B6E86FD1}">
-  <dimension ref="A1:AA85"/>
-  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:BY85"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" style="1" customWidth="1"/>
-    <col min="3" max="7" width="10.83203125" style="1"/>
-    <col min="8" max="12" width="9.6640625" style="1" customWidth="1"/>
-    <col min="13" max="18" width="9.6640625" style="12" customWidth="1"/>
-    <col min="19" max="23" width="10.83203125" style="1"/>
-    <col min="24" max="25" width="10.83203125" style="12"/>
-    <col min="26" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.875" style="1" customWidth="1"/>
+    <col min="3" max="7" width="10.875" style="1"/>
+    <col min="8" max="12" width="9.625" style="1" customWidth="1"/>
+    <col min="13" max="18" width="9.625" style="12" customWidth="1"/>
+    <col min="19" max="23" width="10.875" style="1"/>
+    <col min="24" max="25" width="10.875" style="12"/>
+    <col min="26" max="28" width="10.875" style="1"/>
+    <col min="29" max="29" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:77" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C2" s="17">
         <v>44681</v>
       </c>
@@ -1150,7 +1213,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:77" x14ac:dyDescent="0.2">
       <c r="C3" s="9" t="s">
         <v>77</v>
       </c>
@@ -1214,8 +1277,32 @@
       <c r="Y3" s="12" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="Z3" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA3" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB3" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC3" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="AD3" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE3" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF3" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG3" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>72</v>
       </c>
@@ -1247,7 +1334,7 @@
         <v>49200</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>73</v>
       </c>
@@ -1264,7 +1351,7 @@
         <v>9157.743902439026</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>84</v>
       </c>
@@ -1296,7 +1383,7 @@
         <v>2137</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:77" x14ac:dyDescent="0.2">
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="9"/>
@@ -1307,7 +1394,7 @@
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>64</v>
       </c>
@@ -1325,7 +1412,7 @@
         <v>272.09300000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>65</v>
       </c>
@@ -1343,7 +1430,7 @@
         <v>123.29600000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>66</v>
       </c>
@@ -1361,7 +1448,7 @@
         <v>55.171999999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:77" x14ac:dyDescent="0.2">
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -1372,7 +1459,7 @@
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>67</v>
       </c>
@@ -1390,7 +1477,7 @@
         <v>313.85500000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1408,7 +1495,7 @@
         <v>123.041</v>
       </c>
     </row>
-    <row r="14" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:77" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
@@ -1452,7 +1539,7 @@
       <c r="X14" s="10"/>
       <c r="Y14" s="10"/>
     </row>
-    <row r="15" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:77" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>28</v>
       </c>
@@ -1495,7 +1582,7 @@
       <c r="X15" s="10"/>
       <c r="Y15" s="10"/>
     </row>
-    <row r="16" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:77" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>7</v>
       </c>
@@ -1577,15 +1664,215 @@
         <v>2332</v>
       </c>
       <c r="Z16" s="4">
-        <f>+Y16*1.2</f>
+        <f>+Y16*(1+$AC$36)</f>
         <v>2798.4</v>
       </c>
       <c r="AA16" s="4">
-        <f>+Z16*1.2</f>
+        <f t="shared" ref="AA16:AG16" si="1">+Z16*(1+$AC$36)</f>
         <v>3358.08</v>
       </c>
-    </row>
-    <row r="17" spans="2:27" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="AB16" s="4">
+        <f t="shared" si="1"/>
+        <v>4029.6959999999999</v>
+      </c>
+      <c r="AC16" s="4">
+        <f t="shared" si="1"/>
+        <v>4835.6351999999997</v>
+      </c>
+      <c r="AD16" s="4">
+        <f t="shared" si="1"/>
+        <v>5802.7622399999991</v>
+      </c>
+      <c r="AE16" s="4">
+        <f t="shared" si="1"/>
+        <v>6963.3146879999986</v>
+      </c>
+      <c r="AF16" s="4">
+        <f t="shared" si="1"/>
+        <v>8355.9776255999986</v>
+      </c>
+      <c r="AG16" s="4">
+        <f t="shared" si="1"/>
+        <v>10027.173150719998</v>
+      </c>
+      <c r="AH16" s="4">
+        <f>AG16*(1+$AC$37)</f>
+        <v>10127.444882227199</v>
+      </c>
+      <c r="AI16" s="4">
+        <f t="shared" ref="AI16:BY16" si="2">AH16*(1+$AC$37)</f>
+        <v>10228.719331049471</v>
+      </c>
+      <c r="AJ16" s="4">
+        <f t="shared" si="2"/>
+        <v>10331.006524359966</v>
+      </c>
+      <c r="AK16" s="4">
+        <f t="shared" si="2"/>
+        <v>10434.316589603566</v>
+      </c>
+      <c r="AL16" s="4">
+        <f t="shared" si="2"/>
+        <v>10538.659755499602</v>
+      </c>
+      <c r="AM16" s="4">
+        <f t="shared" si="2"/>
+        <v>10644.046353054599</v>
+      </c>
+      <c r="AN16" s="4">
+        <f t="shared" si="2"/>
+        <v>10750.486816585144</v>
+      </c>
+      <c r="AO16" s="4">
+        <f t="shared" si="2"/>
+        <v>10857.991684750996</v>
+      </c>
+      <c r="AP16" s="4">
+        <f t="shared" si="2"/>
+        <v>10966.571601598505</v>
+      </c>
+      <c r="AQ16" s="4">
+        <f t="shared" si="2"/>
+        <v>11076.23731761449</v>
+      </c>
+      <c r="AR16" s="4">
+        <f t="shared" si="2"/>
+        <v>11186.999690790635</v>
+      </c>
+      <c r="AS16" s="4">
+        <f t="shared" si="2"/>
+        <v>11298.869687698541</v>
+      </c>
+      <c r="AT16" s="4">
+        <f t="shared" si="2"/>
+        <v>11411.858384575527</v>
+      </c>
+      <c r="AU16" s="4">
+        <f t="shared" si="2"/>
+        <v>11525.976968421282</v>
+      </c>
+      <c r="AV16" s="4">
+        <f t="shared" si="2"/>
+        <v>11641.236738105496</v>
+      </c>
+      <c r="AW16" s="4">
+        <f t="shared" si="2"/>
+        <v>11757.649105486551</v>
+      </c>
+      <c r="AX16" s="4">
+        <f t="shared" si="2"/>
+        <v>11875.225596541417</v>
+      </c>
+      <c r="AY16" s="4">
+        <f t="shared" si="2"/>
+        <v>11993.97785250683</v>
+      </c>
+      <c r="AZ16" s="4">
+        <f t="shared" si="2"/>
+        <v>12113.917631031898</v>
+      </c>
+      <c r="BA16" s="4">
+        <f t="shared" si="2"/>
+        <v>12235.056807342216</v>
+      </c>
+      <c r="BB16" s="4">
+        <f t="shared" si="2"/>
+        <v>12357.407375415638</v>
+      </c>
+      <c r="BC16" s="4">
+        <f t="shared" si="2"/>
+        <v>12480.981449169794</v>
+      </c>
+      <c r="BD16" s="4">
+        <f t="shared" si="2"/>
+        <v>12605.791263661493</v>
+      </c>
+      <c r="BE16" s="4">
+        <f t="shared" si="2"/>
+        <v>12731.849176298108</v>
+      </c>
+      <c r="BF16" s="4">
+        <f t="shared" si="2"/>
+        <v>12859.167668061089</v>
+      </c>
+      <c r="BG16" s="4">
+        <f t="shared" si="2"/>
+        <v>12987.7593447417</v>
+      </c>
+      <c r="BH16" s="4">
+        <f t="shared" si="2"/>
+        <v>13117.636938189118</v>
+      </c>
+      <c r="BI16" s="4">
+        <f t="shared" si="2"/>
+        <v>13248.81330757101</v>
+      </c>
+      <c r="BJ16" s="4">
+        <f t="shared" si="2"/>
+        <v>13381.301440646721</v>
+      </c>
+      <c r="BK16" s="4">
+        <f t="shared" si="2"/>
+        <v>13515.114455053188</v>
+      </c>
+      <c r="BL16" s="4">
+        <f t="shared" si="2"/>
+        <v>13650.265599603719</v>
+      </c>
+      <c r="BM16" s="4">
+        <f t="shared" si="2"/>
+        <v>13786.768255599756</v>
+      </c>
+      <c r="BN16" s="4">
+        <f t="shared" si="2"/>
+        <v>13924.635938155754</v>
+      </c>
+      <c r="BO16" s="4">
+        <f t="shared" si="2"/>
+        <v>14063.882297537311</v>
+      </c>
+      <c r="BP16" s="4">
+        <f t="shared" si="2"/>
+        <v>14204.521120512685</v>
+      </c>
+      <c r="BQ16" s="4">
+        <f t="shared" si="2"/>
+        <v>14346.566331717811</v>
+      </c>
+      <c r="BR16" s="4">
+        <f t="shared" si="2"/>
+        <v>14490.031995034989</v>
+      </c>
+      <c r="BS16" s="4">
+        <f t="shared" si="2"/>
+        <v>14634.932314985339</v>
+      </c>
+      <c r="BT16" s="4">
+        <f t="shared" si="2"/>
+        <v>14781.281638135193</v>
+      </c>
+      <c r="BU16" s="4">
+        <f t="shared" si="2"/>
+        <v>14929.094454516546</v>
+      </c>
+      <c r="BV16" s="4">
+        <f t="shared" si="2"/>
+        <v>15078.385399061712</v>
+      </c>
+      <c r="BW16" s="4">
+        <f t="shared" si="2"/>
+        <v>15229.169253052329</v>
+      </c>
+      <c r="BX16" s="4">
+        <f t="shared" si="2"/>
+        <v>15381.460945582852</v>
+      </c>
+      <c r="BY16" s="4">
+        <f t="shared" si="2"/>
+        <v>15535.275555038681</v>
+      </c>
+    </row>
+    <row r="17" spans="2:27" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>30</v>
       </c>
@@ -1623,19 +1910,19 @@
         <v>135.33100000000002</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" ref="N17:Q17" si="1">+N16-N18</f>
+        <f t="shared" ref="N17:Q17" si="3">+N16-N18</f>
         <v>134.68</v>
       </c>
       <c r="O17" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>141.44</v>
       </c>
       <c r="P17" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>148.19999999999999</v>
       </c>
       <c r="Q17" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>154.95999999999998</v>
       </c>
       <c r="R17" s="10">
@@ -1671,36 +1958,36 @@
         <v>839.52</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="3">
-        <f t="shared" ref="C18:I18" si="2">+C16-C17</f>
+        <f t="shared" ref="C18:I18" si="4">+C16-C17</f>
         <v>0</v>
       </c>
       <c r="D18" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>210.82000000000005</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>239.96899999999999</v>
       </c>
       <c r="F18" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>272.15200000000004</v>
       </c>
       <c r="G18" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>270.83099999999996</v>
       </c>
       <c r="H18" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>318.45400000000001</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>325.88</v>
       </c>
       <c r="J18" s="3">
@@ -1768,7 +2055,7 @@
         <v>2518.56</v>
       </c>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>32</v>
       </c>
@@ -1808,19 +2095,19 @@
         <v>221.67180000000002</v>
       </c>
       <c r="O19" s="10">
-        <f t="shared" ref="O19:O21" si="3">+K19*1.05</f>
+        <f t="shared" ref="O19:O21" si="5">+K19*1.05</f>
         <v>230.4162</v>
       </c>
       <c r="P19" s="10">
-        <f t="shared" ref="P19:P21" si="4">+L19*1.05</f>
+        <f t="shared" ref="P19:P21" si="6">+L19*1.05</f>
         <v>232.61595</v>
       </c>
       <c r="Q19" s="10">
-        <f t="shared" ref="Q19:Q21" si="5">+M19*1.05</f>
+        <f t="shared" ref="Q19:Q21" si="7">+M19*1.05</f>
         <v>228.85170000000002</v>
       </c>
       <c r="R19" s="10">
-        <f t="shared" ref="R19:R21" si="6">+N19*1.05</f>
+        <f t="shared" ref="R19:R21" si="8">+N19*1.05</f>
         <v>232.75539000000003</v>
       </c>
       <c r="U19" s="3">
@@ -1830,15 +2117,15 @@
         <v>699.20100000000002</v>
       </c>
       <c r="W19" s="3">
-        <f t="shared" ref="W19:W21" si="7">SUM(G19:J19)</f>
+        <f t="shared" ref="W19:W21" si="9">SUM(G19:J19)</f>
         <v>782.76</v>
       </c>
       <c r="X19" s="10">
-        <f t="shared" ref="X19:X21" si="8">SUM(K19:N19)</f>
+        <f t="shared" ref="X19:X21" si="10">SUM(K19:N19)</f>
         <v>880.60879999999997</v>
       </c>
       <c r="Y19" s="10">
-        <f t="shared" ref="Y19:Y21" si="9">SUM(O19:R19)</f>
+        <f t="shared" ref="Y19:Y21" si="11">SUM(O19:R19)</f>
         <v>924.63924000000009</v>
       </c>
       <c r="Z19" s="3">
@@ -1850,7 +2137,7 @@
         <v>1019.4147621000002</v>
       </c>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>33</v>
       </c>
@@ -1886,23 +2173,23 @@
         <v>151.41</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" ref="N20:N21" si="10">+J20*1.05</f>
+        <f t="shared" ref="N20:N21" si="12">+J20*1.05</f>
         <v>152.83064999999999</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>153.363</v>
       </c>
       <c r="P20" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>156.41535000000002</v>
       </c>
       <c r="Q20" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>158.98050000000001</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>160.4721825</v>
       </c>
       <c r="U20" s="3">
@@ -1912,27 +2199,27 @@
         <v>421.69200000000001</v>
       </c>
       <c r="W20" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>515.94000000000005</v>
       </c>
       <c r="X20" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>599.26765</v>
       </c>
       <c r="Y20" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>629.23103250000008</v>
       </c>
       <c r="Z20" s="3">
-        <f t="shared" ref="Z20:AA20" si="11">+Y20*1.05</f>
+        <f t="shared" ref="Z20:AA20" si="13">+Y20*1.05</f>
         <v>660.69258412500017</v>
       </c>
       <c r="AA20" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>693.72721333125025</v>
       </c>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>34</v>
       </c>
@@ -1968,23 +2255,23 @@
         <v>52.555999999999997</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>60.540900000000001</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>63.573300000000003</v>
       </c>
       <c r="P21" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>53.329500000000003</v>
       </c>
       <c r="Q21" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>55.183799999999998</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>63.567945000000002</v>
       </c>
       <c r="U21" s="3">
@@ -1994,221 +2281,221 @@
         <v>160.49799999999999</v>
       </c>
       <c r="W21" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>193.55799999999999</v>
       </c>
       <c r="X21" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>224.43289999999999</v>
       </c>
       <c r="Y21" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>235.65454500000001</v>
       </c>
       <c r="Z21" s="3">
-        <f t="shared" ref="Z21:AA21" si="12">+Y21*1.05</f>
+        <f t="shared" ref="Z21:AA21" si="14">+Y21*1.05</f>
         <v>247.43727225000004</v>
       </c>
       <c r="AA21" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>259.80913586250006</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C22" s="3">
-        <f t="shared" ref="C22:N22" si="13">SUM(C19:C21)</f>
+        <f t="shared" ref="C22:N22" si="15">SUM(C19:C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>330.226</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>322.89200000000005</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>345.101</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>339.37800000000004</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>367.45699999999999</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>371.096</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>414.327</v>
       </c>
       <c r="K22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>426.05</v>
       </c>
       <c r="L22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>421.29599999999999</v>
       </c>
       <c r="M22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>421.92</v>
       </c>
       <c r="N22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>435.04335000000003</v>
       </c>
       <c r="O22" s="3">
-        <f t="shared" ref="O22:R22" si="14">SUM(O19:O21)</f>
+        <f t="shared" ref="O22:R22" si="16">SUM(O19:O21)</f>
         <v>447.35250000000002</v>
       </c>
       <c r="P22" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>442.36079999999998</v>
       </c>
       <c r="Q22" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>443.01600000000008</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>456.79551750000007</v>
       </c>
       <c r="U22" s="3">
-        <f t="shared" ref="U22" si="15">SUM(U19:U21)</f>
+        <f t="shared" ref="U22" si="17">SUM(U19:U21)</f>
         <v>903.654</v>
       </c>
       <c r="V22" s="3">
-        <f t="shared" ref="V22:W22" si="16">SUM(V19:V21)</f>
+        <f t="shared" ref="V22:W22" si="18">SUM(V19:V21)</f>
         <v>1281.3910000000001</v>
       </c>
       <c r="W22" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1492.258</v>
       </c>
       <c r="X22" s="3">
-        <f t="shared" ref="X22:Y22" si="17">SUM(X19:X21)</f>
+        <f t="shared" ref="X22:Y22" si="19">SUM(X19:X21)</f>
         <v>1704.30935</v>
       </c>
       <c r="Y22" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1789.5248175000004</v>
       </c>
       <c r="Z22" s="3">
-        <f t="shared" ref="Z22:AA22" si="18">SUM(Z19:Z21)</f>
+        <f t="shared" ref="Z22:AA22" si="20">SUM(Z19:Z21)</f>
         <v>1879.0010583750002</v>
       </c>
       <c r="AA22" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1972.9511112937507</v>
       </c>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="3">
-        <f t="shared" ref="C23:N23" si="19">C18-C22</f>
+        <f t="shared" ref="C23:N23" si="21">C18-C22</f>
         <v>0</v>
       </c>
       <c r="D23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-119.40599999999995</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-82.923000000000059</v>
       </c>
       <c r="F23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-72.948999999999955</v>
       </c>
       <c r="G23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-68.547000000000082</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-49.002999999999986</v>
       </c>
       <c r="I23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-45.216000000000008</v>
       </c>
       <c r="J23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-70.966000000000008</v>
       </c>
       <c r="K23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-98.185999999999979</v>
       </c>
       <c r="L23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-71.44</v>
       </c>
       <c r="M23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-27.876000000000033</v>
       </c>
       <c r="N23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-51.723350000000039</v>
       </c>
       <c r="O23" s="3">
-        <f t="shared" ref="O23:R23" si="20">O18-O22</f>
+        <f t="shared" ref="O23:R23" si="22">O18-O22</f>
         <v>-44.792500000000018</v>
       </c>
       <c r="P23" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-20.560799999999972</v>
       </c>
       <c r="Q23" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-1.9760000000000559</v>
       </c>
       <c r="R23" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>3.4844824999998991</v>
       </c>
       <c r="U23" s="3">
-        <f t="shared" ref="U23" si="21">U18-U22</f>
+        <f t="shared" ref="U23" si="23">U18-U22</f>
         <v>-289.36400000000003</v>
       </c>
       <c r="V23" s="3">
-        <f t="shared" ref="V23:W23" si="22">V18-V22</f>
+        <f t="shared" ref="V23:W23" si="24">V18-V22</f>
         <v>-346.6550000000002</v>
       </c>
       <c r="W23" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-233.7320000000002</v>
       </c>
       <c r="X23" s="3">
-        <f t="shared" ref="X23:Y23" si="23">X18-X22</f>
+        <f t="shared" ref="X23:Y23" si="25">X18-X22</f>
         <v>-249.22534999999993</v>
       </c>
       <c r="Y23" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-63.844817500000318</v>
       </c>
       <c r="Z23" s="3">
-        <f t="shared" ref="Z23:AA23" si="24">Z18-Z22</f>
+        <f t="shared" ref="Z23:AA23" si="26">Z18-Z22</f>
         <v>219.798941625</v>
       </c>
       <c r="AA23" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>545.60888870624922</v>
       </c>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>37</v>
       </c>
@@ -2276,15 +2563,15 @@
         <v>13.401</v>
       </c>
       <c r="W24" s="3">
-        <f t="shared" ref="W24" si="25">SUM(G24:J24)</f>
+        <f t="shared" ref="W24" si="27">SUM(G24:J24)</f>
         <v>70.215999999999994</v>
       </c>
       <c r="X24" s="10">
-        <f t="shared" ref="X24" si="26">SUM(K24:N24)</f>
+        <f t="shared" ref="X24" si="28">SUM(K24:N24)</f>
         <v>82.515999999999991</v>
       </c>
       <c r="Y24" s="10">
-        <f t="shared" ref="Y24:Y26" si="27">SUM(O24:R24)</f>
+        <f t="shared" ref="Y24:Y26" si="29">SUM(O24:R24)</f>
         <v>83.067999999999998</v>
       </c>
       <c r="Z24" s="3">
@@ -2296,40 +2583,40 @@
         <v>83.067999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" ref="C25:J25" si="28">+C23+C24</f>
+        <f t="shared" ref="C25:J25" si="30">+C23+C24</f>
         <v>0</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-120.37899999999995</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-79.806000000000054</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-61.483999999999952</v>
       </c>
       <c r="G25" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-51.759000000000086</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-34.008999999999986</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-25.662000000000006</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-52.086000000000013</v>
       </c>
       <c r="K25" s="3">
@@ -2349,51 +2636,51 @@
         <v>-30.95635000000004</v>
       </c>
       <c r="O25" s="3">
-        <f t="shared" ref="O25:R25" si="29">+O23+O24</f>
+        <f t="shared" ref="O25:R25" si="31">+O23+O24</f>
         <v>-24.025500000000019</v>
       </c>
       <c r="P25" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.20620000000002747</v>
       </c>
       <c r="Q25" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>18.790999999999944</v>
       </c>
       <c r="R25" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>24.251482499999899</v>
       </c>
       <c r="U25" s="3">
-        <f t="shared" ref="U25:AA25" si="30">+U23+U24</f>
+        <f t="shared" ref="U25:AA25" si="32">+U23+U24</f>
         <v>-302.88900000000001</v>
       </c>
       <c r="V25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-333.25400000000019</v>
       </c>
       <c r="W25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-163.51600000000019</v>
       </c>
       <c r="X25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-166.70934999999994</v>
       </c>
       <c r="Y25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>19.22318249999968</v>
       </c>
       <c r="Z25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>302.86694162499998</v>
       </c>
       <c r="AA25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>628.6768887062492</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
@@ -2450,15 +2737,15 @@
         <v>12.144</v>
       </c>
       <c r="W26" s="3">
-        <f t="shared" ref="W26" si="31">SUM(G26:J26)</f>
+        <f t="shared" ref="W26" si="33">SUM(G26:J26)</f>
         <v>13.084000000000001</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" ref="X26" si="32">SUM(K26:N26)</f>
+        <f t="shared" ref="X26" si="34">SUM(K26:N26)</f>
         <v>9.1449999999999996</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Z26" s="3">
@@ -2470,40 +2757,40 @@
         <v>125.73537774124985</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="3">
-        <f t="shared" ref="C27:J27" si="33">+C25-C26</f>
+        <f t="shared" ref="C27:J27" si="35">+C25-C26</f>
         <v>0</v>
       </c>
       <c r="D27" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-123.42799999999995</v>
       </c>
       <c r="E27" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-84.841000000000051</v>
       </c>
       <c r="F27" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-64.397999999999954</v>
       </c>
       <c r="G27" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-54.246000000000087</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-37.596999999999987</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-29.297000000000004</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-55.460000000000015</v>
       </c>
       <c r="K27" s="3">
@@ -2523,84 +2810,84 @@
         <v>-30.95635000000004</v>
       </c>
       <c r="O27" s="3">
-        <f t="shared" ref="O27:R27" si="34">+O25-O26</f>
+        <f t="shared" ref="O27:R27" si="36">+O25-O26</f>
         <v>-24.025500000000019</v>
       </c>
       <c r="P27" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.20620000000002747</v>
       </c>
       <c r="Q27" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>18.790999999999944</v>
       </c>
       <c r="R27" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>24.251482499999899</v>
       </c>
       <c r="U27" s="3">
-        <f t="shared" ref="U27:AA27" si="35">+U25-U26</f>
+        <f t="shared" ref="U27:AA27" si="37">+U25-U26</f>
         <v>-306.86599999999999</v>
       </c>
       <c r="V27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-345.3980000000002</v>
       </c>
       <c r="W27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-176.60000000000019</v>
       </c>
       <c r="X27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-175.85434999999995</v>
       </c>
       <c r="Y27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>19.22318249999968</v>
       </c>
       <c r="Z27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>272.58024746249998</v>
       </c>
       <c r="AA27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>502.94151096499934</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="7" t="e">
-        <f t="shared" ref="C28:J28" si="36">C27/C29</f>
+        <f t="shared" ref="C28:J28" si="38">C27/C29</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-1.8062335280774275</v>
       </c>
       <c r="E28" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-1.2310638914773968</v>
       </c>
       <c r="F28" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.92625357140093434</v>
       </c>
       <c r="G28" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.77298280464511981</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.53047574476307036</v>
       </c>
       <c r="I28" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.40940456377438567</v>
       </c>
       <c r="J28" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.76655837267370075</v>
       </c>
       <c r="K28" s="7">
@@ -2620,51 +2907,51 @@
         <v>-0.41821267224919473</v>
       </c>
       <c r="O28" s="7">
-        <f t="shared" ref="O28:R28" si="37">O27/O29</f>
+        <f t="shared" ref="O28:R28" si="39">O27/O29</f>
         <v>-0.32457859395965682</v>
       </c>
       <c r="P28" s="7">
-        <f t="shared" si="37"/>
-        <v>2.7857112682146096E-3</v>
+        <f t="shared" si="39"/>
+        <v>2.5456790123460182E-3</v>
       </c>
       <c r="Q28" s="7">
-        <f t="shared" si="37"/>
-        <v>0.25386178681383897</v>
+        <f t="shared" si="39"/>
+        <v>0.23198765432098695</v>
       </c>
       <c r="R28" s="7">
-        <f t="shared" si="37"/>
-        <v>0.32763156193574261</v>
+        <f t="shared" si="39"/>
+        <v>0.29940101851851725</v>
       </c>
       <c r="U28" s="7">
-        <f t="shared" ref="U28:AA28" si="38">U27/U29</f>
+        <f t="shared" ref="U28:AA28" si="40">U27/U29</f>
         <v>-4.7529676115582671</v>
       </c>
       <c r="V28" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-5.0328824418661222</v>
       </c>
       <c r="W28" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-2.478935809701309</v>
       </c>
       <c r="X28" s="7">
-        <f t="shared" si="38"/>
-        <v>-2.387907960367845</v>
+        <f t="shared" si="40"/>
+        <v>-2.171041358024691</v>
       </c>
       <c r="Y28" s="7">
-        <f t="shared" si="38"/>
-        <v>0.25970046605813707</v>
+        <f t="shared" si="40"/>
+        <v>0.2373232407407368</v>
       </c>
       <c r="Z28" s="7">
-        <f t="shared" si="38"/>
-        <v>3.6824920797716381</v>
+        <f t="shared" si="40"/>
+        <v>3.3651882402777775</v>
       </c>
       <c r="AA28" s="7">
-        <f t="shared" si="38"/>
-        <v>6.7946160734621417</v>
-      </c>
-    </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.35">
+        <f t="shared" si="40"/>
+        <v>6.2091544563580161</v>
+      </c>
+    </row>
+    <row r="29" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
         <v>1</v>
       </c>
@@ -2708,16 +2995,15 @@
         <v>74.020593000000005</v>
       </c>
       <c r="P29" s="10">
-        <f t="shared" ref="P29:R29" si="39">+O29</f>
-        <v>74.020593000000005</v>
+        <v>81</v>
       </c>
       <c r="Q29" s="10">
-        <f t="shared" si="39"/>
-        <v>74.020593000000005</v>
+        <f t="shared" ref="P29:R29" si="41">+P29</f>
+        <v>81</v>
       </c>
       <c r="R29" s="10">
-        <f t="shared" si="39"/>
-        <v>74.020593000000005</v>
+        <f t="shared" si="41"/>
+        <v>81</v>
       </c>
       <c r="U29" s="3">
         <v>64.563032000000007</v>
@@ -2730,191 +3016,189 @@
         <v>71.240247249999996</v>
       </c>
       <c r="X29" s="10">
-        <f>AVERAGE(K29:N29)</f>
-        <v>73.64368850000001</v>
+        <v>81</v>
       </c>
       <c r="Y29" s="10">
-        <f>AVERAGE(O29:R29)</f>
-        <v>74.020593000000005</v>
+        <v>81</v>
       </c>
       <c r="Z29" s="3">
         <f>+Y29</f>
-        <v>74.020593000000005</v>
+        <v>81</v>
       </c>
       <c r="AA29" s="3">
         <f>+Z29</f>
-        <v>74.020593000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
-        <f t="shared" ref="H31:R31" si="40">H16/D16-1</f>
+        <f t="shared" ref="H31:R31" si="42">H16/D16-1</f>
         <v>0.39188825245014303</v>
       </c>
       <c r="I31" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.29769409000032976</v>
       </c>
       <c r="J31" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.26760805065981752</v>
       </c>
       <c r="K31" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.22341968067774531</v>
       </c>
       <c r="L31" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.12817166952578041</v>
       </c>
       <c r="M31" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.22275013974287305</v>
       </c>
       <c r="N31" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.13099942795009634</v>
       </c>
       <c r="O31" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.20738368389629813</v>
       </c>
       <c r="P31" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.19219675847976103</v>
       </c>
       <c r="Q31" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.12585596221959849</v>
       </c>
       <c r="R31" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.20077220077220082</v>
       </c>
       <c r="V31" s="19">
-        <f>+V16/U16-1</f>
+        <f t="shared" ref="V31:AA31" si="43">+V16/U16-1</f>
         <v>0.46951985735572488</v>
       </c>
       <c r="W31" s="19">
-        <f>+W16/V16-1</f>
+        <f t="shared" si="43"/>
         <v>0.31071539827419703</v>
       </c>
       <c r="X31" s="19">
-        <f>+X16/W16-1</f>
+        <f t="shared" si="43"/>
         <v>0.17411294400333688</v>
       </c>
       <c r="Y31" s="19">
-        <f>+Y16/X16-1</f>
+        <f t="shared" si="43"/>
         <v>0.18013506777426613</v>
       </c>
       <c r="Z31" s="19">
-        <f>+Z16/Y16-1</f>
+        <f t="shared" si="43"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AA31" s="19">
-        <f>+AA16/Z16-1</f>
+        <f t="shared" si="43"/>
         <v>0.19999999999999996</v>
       </c>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D32" s="19">
-        <f t="shared" ref="D32:F32" si="41">+D18/D16</f>
+        <f t="shared" ref="D32:F32" si="44">+D18/D16</f>
         <v>0.69241178170734918</v>
       </c>
       <c r="E32" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.71928625596110563</v>
       </c>
       <c r="F32" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.75323266318306625</v>
       </c>
       <c r="G32" s="19">
-        <f t="shared" ref="G32:L32" si="42">+G18/G16</f>
+        <f t="shared" ref="G32:L32" si="45">+G18/G16</f>
         <v>0.73539426523297491</v>
       </c>
       <c r="H32" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.75144115849557924</v>
       </c>
       <c r="I32" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.75271747917715703</v>
       </c>
       <c r="J32" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.74969323278064282</v>
       </c>
       <c r="K32" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.72767949289885281</v>
       </c>
       <c r="L32" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.73174945462227237</v>
       </c>
       <c r="M32" s="19">
-        <f>+M18/M16</f>
+        <f t="shared" ref="M32:R32" si="46">+M18/M16</f>
         <v>0.74435702479338839</v>
       </c>
       <c r="N32" s="19">
-        <f>+N18/N16</f>
+        <f t="shared" si="46"/>
         <v>0.74</v>
       </c>
       <c r="O32" s="19">
-        <f>+O18/O16</f>
+        <f t="shared" si="46"/>
         <v>0.74</v>
       </c>
       <c r="P32" s="19">
-        <f>+P18/P16</f>
+        <f t="shared" si="46"/>
         <v>0.74</v>
       </c>
       <c r="Q32" s="19">
-        <f>+Q18/Q16</f>
+        <f t="shared" si="46"/>
         <v>0.74</v>
       </c>
       <c r="R32" s="19">
-        <f>+R18/R16</f>
+        <f t="shared" si="46"/>
         <v>0.74</v>
       </c>
       <c r="U32" s="19">
-        <f>+U18/U16</f>
+        <f t="shared" ref="U32:AA32" si="47">+U18/U16</f>
         <v>0.703024324144924</v>
       </c>
       <c r="V32" s="19">
-        <f>+V18/V16</f>
+        <f t="shared" si="47"/>
         <v>0.7279648609077598</v>
       </c>
       <c r="W32" s="19">
-        <f>+W18/W16</f>
+        <f t="shared" si="47"/>
         <v>0.74778239714416594</v>
       </c>
       <c r="X32" s="19">
-        <f>+X18/X16</f>
+        <f t="shared" si="47"/>
         <v>0.73636177313775752</v>
       </c>
       <c r="Y32" s="19">
-        <f>+Y18/Y16</f>
+        <f t="shared" si="47"/>
         <v>0.74</v>
       </c>
       <c r="Z32" s="19">
-        <f>+Z18/Z16</f>
+        <f t="shared" si="47"/>
         <v>0.75</v>
       </c>
       <c r="AA32" s="19">
-        <f>+AA18/AA16</f>
+        <f t="shared" si="47"/>
         <v>0.75</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
         <v>99</v>
       </c>
@@ -2923,7 +3207,7 @@
         <v>1177.3720000000001</v>
       </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>3</v>
       </c>
@@ -2949,8 +3233,11 @@
         <f>673.054+1629.038</f>
         <v>2302.0920000000001</v>
       </c>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="AB35" s="22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
         <v>9</v>
       </c>
@@ -2972,8 +3259,14 @@
       <c r="M36" s="10">
         <v>334.62900000000002</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="AB36" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC36" s="5">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>10</v>
       </c>
@@ -2995,8 +3288,14 @@
       <c r="M37" s="10">
         <v>103.715</v>
       </c>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="AB37" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC37" s="5">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
         <v>11</v>
       </c>
@@ -3018,8 +3317,14 @@
       <c r="M38" s="10">
         <v>53.826999999999998</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="AB38" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC38" s="5">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
         <v>12</v>
       </c>
@@ -3041,8 +3346,15 @@
       <c r="M39" s="10">
         <v>47.344999999999999</v>
       </c>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="AB39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC39" s="21">
+        <f>NPV(AC38,U16:BY16)</f>
+        <v>47391.850417467293</v>
+      </c>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
         <v>13</v>
       </c>
@@ -3064,8 +3376,14 @@
       <c r="M40" s="10">
         <v>35.859000000000002</v>
       </c>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="AB40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
         <v>14</v>
       </c>
@@ -3091,8 +3409,15 @@
         <f>69.679+0.963</f>
         <v>70.641999999999996</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="AB41" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC41" s="21">
+        <f>AC39/AC40</f>
+        <v>585.08457305515174</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>15</v>
       </c>
@@ -3114,8 +3439,15 @@
       <c r="M42" s="10">
         <v>5.5750000000000002</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="AB42" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="AC42" s="23">
+        <f>(AC41-Main!J2)/Main!J2</f>
+        <v>0.84884210660162984</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
         <v>16</v>
       </c>
@@ -3138,7 +3470,7 @@
         <v>271.101</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
         <v>17</v>
       </c>
@@ -3165,10 +3497,18 @@
         <v>3224.7849999999994</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:33" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="AB45" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC45" s="24"/>
+      <c r="AD45" s="24"/>
+      <c r="AE45" s="25"/>
+      <c r="AF45" s="25"/>
+      <c r="AG45" s="25"/>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
         <v>18</v>
       </c>
@@ -3190,8 +3530,14 @@
       <c r="M46" s="10">
         <v>11.444000000000001</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="AB46" s="25"/>
+      <c r="AC46" s="25"/>
+      <c r="AD46" s="25"/>
+      <c r="AE46" s="25"/>
+      <c r="AF46" s="25"/>
+      <c r="AG46" s="25"/>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
         <v>19</v>
       </c>
@@ -3213,8 +3559,14 @@
       <c r="M47" s="10">
         <v>120.598</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="AB47" s="25"/>
+      <c r="AC47" s="25"/>
+      <c r="AD47" s="25"/>
+      <c r="AE47" s="25"/>
+      <c r="AF47" s="25"/>
+      <c r="AG47" s="25"/>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
         <v>20</v>
       </c>
@@ -3240,8 +3592,14 @@
         <f>10.787+27.639</f>
         <v>38.426000000000002</v>
       </c>
-    </row>
-    <row r="49" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="AB48" s="25"/>
+      <c r="AC48" s="25"/>
+      <c r="AD48" s="25"/>
+      <c r="AE48" s="25"/>
+      <c r="AF48" s="25"/>
+      <c r="AG48" s="25"/>
+    </row>
+    <row r="49" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
         <v>21</v>
       </c>
@@ -3264,7 +3622,7 @@
         <v>86.795000000000002</v>
       </c>
     </row>
-    <row r="50" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
         <v>22</v>
       </c>
@@ -3291,7 +3649,7 @@
         <v>304.91199999999998</v>
       </c>
     </row>
-    <row r="51" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
         <v>23</v>
       </c>
@@ -3315,7 +3673,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="52" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
         <v>4</v>
       </c>
@@ -3338,7 +3696,7 @@
         <v>1124.72</v>
       </c>
     </row>
-    <row r="53" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
         <v>24</v>
       </c>
@@ -3361,7 +3719,7 @@
         <v>34.884</v>
       </c>
     </row>
-    <row r="54" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
         <v>25</v>
       </c>
@@ -3384,7 +3742,7 @@
         <v>1501.9760000000001</v>
       </c>
     </row>
-    <row r="55" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
         <v>26</v>
       </c>
@@ -3411,11 +3769,11 @@
         <v>3224.7849999999999</v>
       </c>
     </row>
-    <row r="56" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:25" x14ac:dyDescent="0.2">
       <c r="L56" s="3"/>
       <c r="M56" s="10"/>
     </row>
-    <row r="57" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
         <v>48</v>
       </c>
@@ -3433,15 +3791,15 @@
         <v>-9.7760000000000336</v>
       </c>
       <c r="U57" s="10">
-        <f t="shared" ref="U57:X57" si="43">+U27</f>
+        <f t="shared" ref="U57:W57" si="48">+U27</f>
         <v>-306.86599999999999</v>
       </c>
       <c r="V57" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="48"/>
         <v>-345.3980000000002</v>
       </c>
       <c r="W57" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="48"/>
         <v>-176.60000000000019</v>
       </c>
       <c r="X57" s="10">
@@ -3453,7 +3811,7 @@
         <v>19.22318249999968</v>
       </c>
     </row>
-    <row r="58" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
         <v>49</v>
       </c>
@@ -3478,7 +3836,7 @@
         <v>-176.6</v>
       </c>
     </row>
-    <row r="59" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
         <v>46</v>
       </c>
@@ -3503,7 +3861,7 @@
         <v>18.939</v>
       </c>
     </row>
-    <row r="60" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
         <v>45</v>
       </c>
@@ -3528,7 +3886,7 @@
         <v>456.90699999999998</v>
       </c>
     </row>
-    <row r="61" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
         <v>47</v>
       </c>
@@ -3558,7 +3916,7 @@
         <v>16.579000000000001</v>
       </c>
     </row>
-    <row r="62" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
         <v>52</v>
       </c>
@@ -3583,7 +3941,7 @@
         <v>-1.5740000000000001</v>
       </c>
     </row>
-    <row r="63" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B63" s="1" t="s">
         <v>53</v>
       </c>
@@ -3613,7 +3971,7 @@
         <v>-43.797999999999995</v>
       </c>
     </row>
-    <row r="64" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
         <v>50</v>
       </c>
@@ -3643,7 +4001,7 @@
         <v>-148.97599999999997</v>
       </c>
     </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
         <v>44</v>
       </c>
@@ -3677,11 +4035,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="L66" s="3"/>
       <c r="M66" s="10"/>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
         <v>54</v>
       </c>
@@ -3707,7 +4065,7 @@
       </c>
       <c r="X67" s="10"/>
     </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B68" s="1" t="s">
         <v>98</v>
       </c>
@@ -3726,7 +4084,7 @@
       </c>
       <c r="X68" s="10"/>
     </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B69" s="1" t="s">
         <v>55</v>
       </c>
@@ -3757,7 +4115,7 @@
       </c>
       <c r="X69" s="10"/>
     </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B70" s="1" t="s">
         <v>56</v>
       </c>
@@ -3788,13 +4146,13 @@
       </c>
       <c r="X70" s="10"/>
     </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="F71" s="3"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="10"/>
     </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B72" s="1" t="s">
         <v>57</v>
       </c>
@@ -3810,7 +4168,7 @@
         <v>0.315</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B73" s="1" t="s">
         <v>92</v>
       </c>
@@ -3826,7 +4184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
         <v>13</v>
       </c>
@@ -3842,7 +4200,7 @@
         <v>-0.89500000000000002</v>
       </c>
     </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B75" s="1" t="s">
         <v>58</v>
       </c>
@@ -3860,7 +4218,7 @@
         <v>-0.58000000000000007</v>
       </c>
     </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B76" s="1" t="s">
         <v>51</v>
       </c>
@@ -3876,7 +4234,7 @@
         <v>-0.27400000000000002</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B77" s="1" t="s">
         <v>93</v>
       </c>
@@ -3894,12 +4252,12 @@
         <v>-616.81700000000001</v>
       </c>
     </row>
-    <row r="78" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:24" x14ac:dyDescent="0.2">
       <c r="F78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
     </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>68</v>
       </c>
@@ -3918,18 +4276,18 @@
       </c>
       <c r="L79" s="3"/>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="F80" s="5"/>
       <c r="K80" s="5">
         <f>+K79/G79-1</f>
         <v>0.15153523304616745</v>
       </c>
     </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:23" x14ac:dyDescent="0.2">
       <c r="F81" s="5"/>
       <c r="K81" s="5"/>
     </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B82" s="1" t="s">
         <v>32</v>
       </c>
@@ -3947,7 +4305,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B85" s="1" t="s">
         <v>94</v>
       </c>
@@ -3964,19 +4322,23 @@
         <v>35.457000000000001</v>
       </c>
       <c r="U85" s="3">
-        <f t="shared" ref="U85:W85" si="44">+U65+U67</f>
+        <f t="shared" ref="U85:W85" si="49">+U65+U67</f>
         <v>-1.0920000000000236</v>
       </c>
       <c r="V85" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>-20.21399999999997</v>
       </c>
       <c r="W85" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>113.405</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="AB45:AD45"/>
+  </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{C133F01A-E3DB-8640-9562-7A3F4F520D71}"/>
   </hyperlinks>

--- a/MDB.xlsx
+++ b/MDB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41A1735-D2B9-484F-B635-DC603A79CD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A6420E-818E-4DBB-AA5D-CCA58FA4EA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="105" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{9A102858-C73E-5D48-A2CD-E1A822063168}"/>
+    <workbookView xWindow="40305" yWindow="90" windowWidth="11310" windowHeight="20805" activeTab="1" xr2:uid="{9A102858-C73E-5D48-A2CD-E1A822063168}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -506,7 +506,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -552,6 +552,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1630,20 +1633,18 @@
         <v>518</v>
       </c>
       <c r="O16" s="4">
-        <f>+N16+26</f>
-        <v>544</v>
+        <v>549.01400000000001</v>
       </c>
       <c r="P16" s="4">
-        <f>+O16+26</f>
-        <v>570</v>
+        <v>591.40200000000004</v>
       </c>
       <c r="Q16" s="4">
         <f>+P16+26</f>
-        <v>596</v>
+        <v>617.40200000000004</v>
       </c>
       <c r="R16" s="4">
         <f>+Q16+26</f>
-        <v>622</v>
+        <v>643.40200000000004</v>
       </c>
       <c r="U16" s="4">
         <v>873.78200000000004</v>
@@ -1661,215 +1662,215 @@
       </c>
       <c r="Y16" s="13">
         <f>SUM(O16:R16)</f>
-        <v>2332</v>
+        <v>2401.2200000000003</v>
       </c>
       <c r="Z16" s="4">
         <f>+Y16*(1+$AC$36)</f>
-        <v>2798.4</v>
+        <v>2881.4640000000004</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" ref="AA16:AG16" si="1">+Z16*(1+$AC$36)</f>
-        <v>3358.08</v>
+        <v>3457.7568000000006</v>
       </c>
       <c r="AB16" s="4">
         <f t="shared" si="1"/>
-        <v>4029.6959999999999</v>
+        <v>4149.3081600000005</v>
       </c>
       <c r="AC16" s="4">
         <f t="shared" si="1"/>
-        <v>4835.6351999999997</v>
+        <v>4979.1697920000006</v>
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="1"/>
-        <v>5802.7622399999991</v>
+        <v>5975.0037504000002</v>
       </c>
       <c r="AE16" s="4">
         <f t="shared" si="1"/>
-        <v>6963.3146879999986</v>
+        <v>7170.0045004800004</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="1"/>
-        <v>8355.9776255999986</v>
+        <v>8604.0054005759994</v>
       </c>
       <c r="AG16" s="4">
         <f t="shared" si="1"/>
-        <v>10027.173150719998</v>
+        <v>10324.806480691199</v>
       </c>
       <c r="AH16" s="4">
         <f>AG16*(1+$AC$37)</f>
-        <v>10127.444882227199</v>
+        <v>10428.054545498111</v>
       </c>
       <c r="AI16" s="4">
         <f t="shared" ref="AI16:BY16" si="2">AH16*(1+$AC$37)</f>
-        <v>10228.719331049471</v>
+        <v>10532.335090953093</v>
       </c>
       <c r="AJ16" s="4">
         <f t="shared" si="2"/>
-        <v>10331.006524359966</v>
+        <v>10637.658441862624</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="2"/>
-        <v>10434.316589603566</v>
+        <v>10744.03502628125</v>
       </c>
       <c r="AL16" s="4">
         <f t="shared" si="2"/>
-        <v>10538.659755499602</v>
+        <v>10851.475376544062</v>
       </c>
       <c r="AM16" s="4">
         <f t="shared" si="2"/>
-        <v>10644.046353054599</v>
+        <v>10959.990130309503</v>
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="2"/>
-        <v>10750.486816585144</v>
+        <v>11069.590031612599</v>
       </c>
       <c r="AO16" s="4">
         <f t="shared" si="2"/>
-        <v>10857.991684750996</v>
+        <v>11180.285931928725</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="2"/>
-        <v>10966.571601598505</v>
+        <v>11292.088791248012</v>
       </c>
       <c r="AQ16" s="4">
         <f t="shared" si="2"/>
-        <v>11076.23731761449</v>
+        <v>11405.009679160492</v>
       </c>
       <c r="AR16" s="4">
         <f t="shared" si="2"/>
-        <v>11186.999690790635</v>
+        <v>11519.059775952097</v>
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="2"/>
-        <v>11298.869687698541</v>
+        <v>11634.250373711619</v>
       </c>
       <c r="AT16" s="4">
         <f t="shared" si="2"/>
-        <v>11411.858384575527</v>
+        <v>11750.592877448735</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="2"/>
-        <v>11525.976968421282</v>
+        <v>11868.098806223223</v>
       </c>
       <c r="AV16" s="4">
         <f t="shared" si="2"/>
-        <v>11641.236738105496</v>
+        <v>11986.779794285456</v>
       </c>
       <c r="AW16" s="4">
         <f t="shared" si="2"/>
-        <v>11757.649105486551</v>
+        <v>12106.64759222831</v>
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="2"/>
-        <v>11875.225596541417</v>
+        <v>12227.714068150593</v>
       </c>
       <c r="AY16" s="4">
         <f t="shared" si="2"/>
-        <v>11993.97785250683</v>
+        <v>12349.9912088321</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="2"/>
-        <v>12113.917631031898</v>
+        <v>12473.49112092042</v>
       </c>
       <c r="BA16" s="4">
         <f t="shared" si="2"/>
-        <v>12235.056807342216</v>
+        <v>12598.226032129625</v>
       </c>
       <c r="BB16" s="4">
         <f t="shared" si="2"/>
-        <v>12357.407375415638</v>
+        <v>12724.208292450921</v>
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="2"/>
-        <v>12480.981449169794</v>
+        <v>12851.450375375431</v>
       </c>
       <c r="BD16" s="4">
         <f t="shared" si="2"/>
-        <v>12605.791263661493</v>
+        <v>12979.964879129186</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="2"/>
-        <v>12731.849176298108</v>
+        <v>13109.764527920477</v>
       </c>
       <c r="BF16" s="4">
         <f t="shared" si="2"/>
-        <v>12859.167668061089</v>
+        <v>13240.862173199683</v>
       </c>
       <c r="BG16" s="4">
         <f t="shared" si="2"/>
-        <v>12987.7593447417</v>
+        <v>13373.270794931679</v>
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="2"/>
-        <v>13117.636938189118</v>
+        <v>13507.003502880996</v>
       </c>
       <c r="BI16" s="4">
         <f t="shared" si="2"/>
-        <v>13248.81330757101</v>
+        <v>13642.073537909806</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="2"/>
-        <v>13381.301440646721</v>
+        <v>13778.494273288905</v>
       </c>
       <c r="BK16" s="4">
         <f t="shared" si="2"/>
-        <v>13515.114455053188</v>
+        <v>13916.279216021794</v>
       </c>
       <c r="BL16" s="4">
         <f t="shared" si="2"/>
-        <v>13650.265599603719</v>
+        <v>14055.442008182012</v>
       </c>
       <c r="BM16" s="4">
         <f t="shared" si="2"/>
-        <v>13786.768255599756</v>
+        <v>14195.996428263832</v>
       </c>
       <c r="BN16" s="4">
         <f t="shared" si="2"/>
-        <v>13924.635938155754</v>
+        <v>14337.95639254647</v>
       </c>
       <c r="BO16" s="4">
         <f t="shared" si="2"/>
-        <v>14063.882297537311</v>
+        <v>14481.335956471934</v>
       </c>
       <c r="BP16" s="4">
         <f t="shared" si="2"/>
-        <v>14204.521120512685</v>
+        <v>14626.149316036654</v>
       </c>
       <c r="BQ16" s="4">
         <f t="shared" si="2"/>
-        <v>14346.566331717811</v>
+        <v>14772.410809197021</v>
       </c>
       <c r="BR16" s="4">
         <f t="shared" si="2"/>
-        <v>14490.031995034989</v>
+        <v>14920.134917288991</v>
       </c>
       <c r="BS16" s="4">
         <f t="shared" si="2"/>
-        <v>14634.932314985339</v>
+        <v>15069.336266461882</v>
       </c>
       <c r="BT16" s="4">
         <f t="shared" si="2"/>
-        <v>14781.281638135193</v>
+        <v>15220.0296291265</v>
       </c>
       <c r="BU16" s="4">
         <f t="shared" si="2"/>
-        <v>14929.094454516546</v>
+        <v>15372.229925417765</v>
       </c>
       <c r="BV16" s="4">
         <f t="shared" si="2"/>
-        <v>15078.385399061712</v>
+        <v>15525.952224671943</v>
       </c>
       <c r="BW16" s="4">
         <f t="shared" si="2"/>
-        <v>15229.169253052329</v>
+        <v>15681.211746918661</v>
       </c>
       <c r="BX16" s="4">
         <f t="shared" si="2"/>
-        <v>15381.460945582852</v>
+        <v>15838.023864387847</v>
       </c>
       <c r="BY16" s="4">
         <f t="shared" si="2"/>
-        <v>15535.275555038681</v>
+        <v>15996.404103031726</v>
       </c>
     </row>
     <row r="17" spans="2:27" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1914,20 +1915,19 @@
         <v>134.68</v>
       </c>
       <c r="O17" s="10">
-        <f t="shared" si="3"/>
-        <v>141.44</v>
+        <v>158.041</v>
       </c>
       <c r="P17" s="10">
-        <f t="shared" si="3"/>
-        <v>148.19999999999999</v>
+        <f>139.949+31.479</f>
+        <v>171.428</v>
       </c>
       <c r="Q17" s="10">
         <f t="shared" si="3"/>
-        <v>154.95999999999998</v>
+        <v>160.52452</v>
       </c>
       <c r="R17" s="10">
         <f>+R16-R18</f>
-        <v>161.72000000000003</v>
+        <v>167.28452000000004</v>
       </c>
       <c r="U17" s="3">
         <f>217.901+41.591</f>
@@ -1947,15 +1947,15 @@
       </c>
       <c r="Y17" s="10">
         <f>SUM(O17:R17)</f>
-        <v>606.31999999999994</v>
+        <v>657.27804000000003</v>
       </c>
       <c r="Z17" s="3">
         <f>+Z16-Z18</f>
-        <v>699.59999999999991</v>
+        <v>720.36599999999999</v>
       </c>
       <c r="AA17" s="3">
         <f>+AA16-AA18</f>
-        <v>839.52</v>
+        <v>864.43920000000026</v>
       </c>
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.2">
@@ -2011,20 +2011,20 @@
         <v>383.32</v>
       </c>
       <c r="O18" s="10">
-        <f>+O16*0.74</f>
-        <v>402.56</v>
+        <f>O16-O17</f>
+        <v>390.97300000000001</v>
       </c>
       <c r="P18" s="10">
-        <f>+P16*0.74</f>
-        <v>421.8</v>
+        <f>P16-P17</f>
+        <v>419.97400000000005</v>
       </c>
       <c r="Q18" s="10">
         <f>+Q16*0.74</f>
-        <v>441.04</v>
+        <v>456.87748000000005</v>
       </c>
       <c r="R18" s="10">
         <f>+R16*0.74</f>
-        <v>460.28</v>
+        <v>476.11748</v>
       </c>
       <c r="U18" s="3">
         <f>+U16-U17</f>
@@ -2044,15 +2044,15 @@
       </c>
       <c r="Y18" s="10">
         <f>+Y16-Y17</f>
-        <v>1725.68</v>
+        <v>1743.9419600000001</v>
       </c>
       <c r="Z18" s="3">
         <f>+Z16*0.75</f>
-        <v>2098.8000000000002</v>
+        <v>2161.0980000000004</v>
       </c>
       <c r="AA18" s="3">
         <f>+AA16*0.75</f>
-        <v>2518.56</v>
+        <v>2593.3176000000003</v>
       </c>
     </row>
     <row r="19" spans="2:27" x14ac:dyDescent="0.2">
@@ -2095,19 +2095,17 @@
         <v>221.67180000000002</v>
       </c>
       <c r="O19" s="10">
-        <f t="shared" ref="O19:O21" si="5">+K19*1.05</f>
-        <v>230.4162</v>
+        <v>220.923</v>
       </c>
       <c r="P19" s="10">
-        <f t="shared" ref="P19:P21" si="6">+L19*1.05</f>
-        <v>232.61595</v>
+        <v>244.065</v>
       </c>
       <c r="Q19" s="10">
-        <f t="shared" ref="Q19:Q21" si="7">+M19*1.05</f>
+        <f t="shared" ref="Q19:Q21" si="5">+M19*1.05</f>
         <v>228.85170000000002</v>
       </c>
       <c r="R19" s="10">
-        <f t="shared" ref="R19:R21" si="8">+N19*1.05</f>
+        <f t="shared" ref="R19:R21" si="6">+N19*1.05</f>
         <v>232.75539000000003</v>
       </c>
       <c r="U19" s="3">
@@ -2117,24 +2115,24 @@
         <v>699.20100000000002</v>
       </c>
       <c r="W19" s="3">
-        <f t="shared" ref="W19:W21" si="9">SUM(G19:J19)</f>
+        <f t="shared" ref="W19:W21" si="7">SUM(G19:J19)</f>
         <v>782.76</v>
       </c>
       <c r="X19" s="10">
-        <f t="shared" ref="X19:X21" si="10">SUM(K19:N19)</f>
+        <f t="shared" ref="X19:X21" si="8">SUM(K19:N19)</f>
         <v>880.60879999999997</v>
       </c>
       <c r="Y19" s="10">
-        <f t="shared" ref="Y19:Y21" si="11">SUM(O19:R19)</f>
-        <v>924.63924000000009</v>
+        <f t="shared" ref="Y19:Y21" si="9">SUM(O19:R19)</f>
+        <v>926.59509000000003</v>
       </c>
       <c r="Z19" s="3">
         <f>+Y19*1.05</f>
-        <v>970.87120200000015</v>
+        <v>972.92484450000006</v>
       </c>
       <c r="AA19" s="3">
         <f>+Z19*1.05</f>
-        <v>1019.4147621000002</v>
+        <v>1021.5710867250001</v>
       </c>
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.2">
@@ -2173,23 +2171,21 @@
         <v>151.41</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" ref="N20:N21" si="12">+J20*1.05</f>
+        <f t="shared" ref="N20:N21" si="10">+J20*1.05</f>
         <v>152.83064999999999</v>
       </c>
       <c r="O20" s="10">
+        <v>168.82900000000001</v>
+      </c>
+      <c r="P20" s="10">
+        <v>181.739</v>
+      </c>
+      <c r="Q20" s="10">
         <f t="shared" si="5"/>
-        <v>153.363</v>
-      </c>
-      <c r="P20" s="10">
+        <v>158.98050000000001</v>
+      </c>
+      <c r="R20" s="10">
         <f t="shared" si="6"/>
-        <v>156.41535000000002</v>
-      </c>
-      <c r="Q20" s="10">
-        <f t="shared" si="7"/>
-        <v>158.98050000000001</v>
-      </c>
-      <c r="R20" s="10">
-        <f t="shared" si="8"/>
         <v>160.4721825</v>
       </c>
       <c r="U20" s="3">
@@ -2199,24 +2195,24 @@
         <v>421.69200000000001</v>
       </c>
       <c r="W20" s="3">
+        <f t="shared" si="7"/>
+        <v>515.94000000000005</v>
+      </c>
+      <c r="X20" s="10">
+        <f t="shared" si="8"/>
+        <v>599.26765</v>
+      </c>
+      <c r="Y20" s="10">
         <f t="shared" si="9"/>
-        <v>515.94000000000005</v>
-      </c>
-      <c r="X20" s="10">
-        <f t="shared" si="10"/>
-        <v>599.26765</v>
-      </c>
-      <c r="Y20" s="10">
+        <v>670.02068250000002</v>
+      </c>
+      <c r="Z20" s="3">
+        <f t="shared" ref="Z20:AA20" si="11">+Y20*1.05</f>
+        <v>703.52171662500007</v>
+      </c>
+      <c r="AA20" s="3">
         <f t="shared" si="11"/>
-        <v>629.23103250000008</v>
-      </c>
-      <c r="Z20" s="3">
-        <f t="shared" ref="Z20:AA20" si="13">+Y20*1.05</f>
-        <v>660.69258412500017</v>
-      </c>
-      <c r="AA20" s="3">
-        <f t="shared" si="13"/>
-        <v>693.72721333125025</v>
+        <v>738.69780245625009</v>
       </c>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.2">
@@ -2255,23 +2251,21 @@
         <v>52.555999999999997</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>60.540900000000001</v>
       </c>
       <c r="O21" s="10">
+        <v>54.774999999999999</v>
+      </c>
+      <c r="P21" s="10">
+        <v>59.463999999999999</v>
+      </c>
+      <c r="Q21" s="10">
         <f t="shared" si="5"/>
-        <v>63.573300000000003</v>
-      </c>
-      <c r="P21" s="10">
+        <v>55.183799999999998</v>
+      </c>
+      <c r="R21" s="10">
         <f t="shared" si="6"/>
-        <v>53.329500000000003</v>
-      </c>
-      <c r="Q21" s="10">
-        <f t="shared" si="7"/>
-        <v>55.183799999999998</v>
-      </c>
-      <c r="R21" s="10">
-        <f t="shared" si="8"/>
         <v>63.567945000000002</v>
       </c>
       <c r="U21" s="3">
@@ -2281,24 +2275,24 @@
         <v>160.49799999999999</v>
       </c>
       <c r="W21" s="3">
+        <f t="shared" si="7"/>
+        <v>193.55799999999999</v>
+      </c>
+      <c r="X21" s="10">
+        <f t="shared" si="8"/>
+        <v>224.43289999999999</v>
+      </c>
+      <c r="Y21" s="10">
         <f t="shared" si="9"/>
-        <v>193.55799999999999</v>
-      </c>
-      <c r="X21" s="10">
-        <f t="shared" si="10"/>
-        <v>224.43289999999999</v>
-      </c>
-      <c r="Y21" s="10">
-        <f t="shared" si="11"/>
-        <v>235.65454500000001</v>
+        <v>232.990745</v>
       </c>
       <c r="Z21" s="3">
-        <f t="shared" ref="Z21:AA21" si="14">+Y21*1.05</f>
-        <v>247.43727225000004</v>
+        <f t="shared" ref="Z21:AA21" si="12">+Y21*1.05</f>
+        <v>244.64028225000001</v>
       </c>
       <c r="AA21" s="3">
-        <f t="shared" si="14"/>
-        <v>259.80913586250006</v>
+        <f t="shared" si="12"/>
+        <v>256.87229636250004</v>
       </c>
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.2">
@@ -2306,96 +2300,96 @@
         <v>35</v>
       </c>
       <c r="C22" s="3">
-        <f t="shared" ref="C22:N22" si="15">SUM(C19:C21)</f>
+        <f t="shared" ref="C22:N22" si="13">SUM(C19:C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>330.226</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>322.89200000000005</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>345.101</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>339.37800000000004</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>367.45699999999999</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>371.096</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>414.327</v>
       </c>
       <c r="K22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>426.05</v>
       </c>
       <c r="L22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>421.29599999999999</v>
       </c>
       <c r="M22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>421.92</v>
       </c>
       <c r="N22" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>435.04335000000003</v>
       </c>
       <c r="O22" s="3">
-        <f t="shared" ref="O22:R22" si="16">SUM(O19:O21)</f>
-        <v>447.35250000000002</v>
+        <f t="shared" ref="O22:R22" si="14">SUM(O19:O21)</f>
+        <v>444.52699999999999</v>
       </c>
       <c r="P22" s="3">
+        <f t="shared" si="14"/>
+        <v>485.26799999999997</v>
+      </c>
+      <c r="Q22" s="3">
+        <f t="shared" si="14"/>
+        <v>443.01600000000008</v>
+      </c>
+      <c r="R22" s="3">
+        <f t="shared" si="14"/>
+        <v>456.79551750000007</v>
+      </c>
+      <c r="U22" s="3">
+        <f t="shared" ref="U22" si="15">SUM(U19:U21)</f>
+        <v>903.654</v>
+      </c>
+      <c r="V22" s="3">
+        <f t="shared" ref="V22:W22" si="16">SUM(V19:V21)</f>
+        <v>1281.3910000000001</v>
+      </c>
+      <c r="W22" s="3">
         <f t="shared" si="16"/>
-        <v>442.36079999999998</v>
-      </c>
-      <c r="Q22" s="3">
-        <f t="shared" si="16"/>
-        <v>443.01600000000008</v>
-      </c>
-      <c r="R22" s="3">
-        <f t="shared" si="16"/>
-        <v>456.79551750000007</v>
-      </c>
-      <c r="U22" s="3">
-        <f t="shared" ref="U22" si="17">SUM(U19:U21)</f>
-        <v>903.654</v>
-      </c>
-      <c r="V22" s="3">
-        <f t="shared" ref="V22:W22" si="18">SUM(V19:V21)</f>
-        <v>1281.3910000000001</v>
-      </c>
-      <c r="W22" s="3">
+        <v>1492.258</v>
+      </c>
+      <c r="X22" s="3">
+        <f t="shared" ref="X22:Y22" si="17">SUM(X19:X21)</f>
+        <v>1704.30935</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="17"/>
+        <v>1829.6065175000001</v>
+      </c>
+      <c r="Z22" s="3">
+        <f t="shared" ref="Z22:AA22" si="18">SUM(Z19:Z21)</f>
+        <v>1921.0868433750002</v>
+      </c>
+      <c r="AA22" s="3">
         <f t="shared" si="18"/>
-        <v>1492.258</v>
-      </c>
-      <c r="X22" s="3">
-        <f t="shared" ref="X22:Y22" si="19">SUM(X19:X21)</f>
-        <v>1704.30935</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="19"/>
-        <v>1789.5248175000004</v>
-      </c>
-      <c r="Z22" s="3">
-        <f t="shared" ref="Z22:AA22" si="20">SUM(Z19:Z21)</f>
-        <v>1879.0010583750002</v>
-      </c>
-      <c r="AA22" s="3">
-        <f t="shared" si="20"/>
-        <v>1972.9511112937507</v>
+        <v>2017.1411855437502</v>
       </c>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.2">
@@ -2403,96 +2397,96 @@
         <v>36</v>
       </c>
       <c r="C23" s="3">
-        <f t="shared" ref="C23:N23" si="21">C18-C22</f>
+        <f t="shared" ref="C23:N23" si="19">C18-C22</f>
         <v>0</v>
       </c>
       <c r="D23" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-119.40599999999995</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-82.923000000000059</v>
       </c>
       <c r="F23" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-72.948999999999955</v>
       </c>
       <c r="G23" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-68.547000000000082</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-49.002999999999986</v>
       </c>
       <c r="I23" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-45.216000000000008</v>
       </c>
       <c r="J23" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-70.966000000000008</v>
       </c>
       <c r="K23" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-98.185999999999979</v>
       </c>
       <c r="L23" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-71.44</v>
       </c>
       <c r="M23" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-27.876000000000033</v>
       </c>
       <c r="N23" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>-51.723350000000039</v>
       </c>
       <c r="O23" s="3">
-        <f t="shared" ref="O23:R23" si="22">O18-O22</f>
-        <v>-44.792500000000018</v>
+        <f t="shared" ref="O23:R23" si="20">O18-O22</f>
+        <v>-53.553999999999974</v>
       </c>
       <c r="P23" s="3">
+        <f t="shared" si="20"/>
+        <v>-65.293999999999926</v>
+      </c>
+      <c r="Q23" s="3">
+        <f t="shared" si="20"/>
+        <v>13.861479999999972</v>
+      </c>
+      <c r="R23" s="3">
+        <f t="shared" si="20"/>
+        <v>19.321962499999927</v>
+      </c>
+      <c r="U23" s="3">
+        <f t="shared" ref="U23" si="21">U18-U22</f>
+        <v>-289.36400000000003</v>
+      </c>
+      <c r="V23" s="3">
+        <f t="shared" ref="V23:W23" si="22">V18-V22</f>
+        <v>-346.6550000000002</v>
+      </c>
+      <c r="W23" s="3">
         <f t="shared" si="22"/>
-        <v>-20.560799999999972</v>
-      </c>
-      <c r="Q23" s="3">
-        <f t="shared" si="22"/>
-        <v>-1.9760000000000559</v>
-      </c>
-      <c r="R23" s="3">
-        <f t="shared" si="22"/>
-        <v>3.4844824999998991</v>
-      </c>
-      <c r="U23" s="3">
-        <f t="shared" ref="U23" si="23">U18-U22</f>
-        <v>-289.36400000000003</v>
-      </c>
-      <c r="V23" s="3">
-        <f t="shared" ref="V23:W23" si="24">V18-V22</f>
-        <v>-346.6550000000002</v>
-      </c>
-      <c r="W23" s="3">
+        <v>-233.7320000000002</v>
+      </c>
+      <c r="X23" s="3">
+        <f t="shared" ref="X23:Y23" si="23">X18-X22</f>
+        <v>-249.22534999999993</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="23"/>
+        <v>-85.664557500000001</v>
+      </c>
+      <c r="Z23" s="3">
+        <f t="shared" ref="Z23:AA23" si="24">Z18-Z22</f>
+        <v>240.01115662500024</v>
+      </c>
+      <c r="AA23" s="3">
         <f t="shared" si="24"/>
-        <v>-233.7320000000002</v>
-      </c>
-      <c r="X23" s="3">
-        <f t="shared" ref="X23:Y23" si="25">X18-X22</f>
-        <v>-249.22534999999993</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="25"/>
-        <v>-63.844817500000318</v>
-      </c>
-      <c r="Z23" s="3">
-        <f t="shared" ref="Z23:AA23" si="26">Z18-Z22</f>
-        <v>219.798941625</v>
-      </c>
-      <c r="AA23" s="3">
-        <f t="shared" si="26"/>
-        <v>545.60888870624922</v>
+        <v>576.17641445625009</v>
       </c>
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.2">
@@ -2539,20 +2533,20 @@
         <v>20.766999999999999</v>
       </c>
       <c r="O24" s="10">
-        <f>+N24</f>
-        <v>20.766999999999999</v>
+        <f>23.458-1.066-2.162</f>
+        <v>20.23</v>
       </c>
       <c r="P24" s="10">
-        <f>+O24</f>
-        <v>20.766999999999999</v>
+        <f>23.637-1.473</f>
+        <v>22.164000000000001</v>
       </c>
       <c r="Q24" s="10">
         <f>+P24</f>
-        <v>20.766999999999999</v>
+        <v>22.164000000000001</v>
       </c>
       <c r="R24" s="10">
         <f>+Q24</f>
-        <v>20.766999999999999</v>
+        <v>22.164000000000001</v>
       </c>
       <c r="U24" s="3">
         <f>0.926-11.316-3.135</f>
@@ -2563,24 +2557,24 @@
         <v>13.401</v>
       </c>
       <c r="W24" s="3">
-        <f t="shared" ref="W24" si="27">SUM(G24:J24)</f>
+        <f t="shared" ref="W24" si="25">SUM(G24:J24)</f>
         <v>70.215999999999994</v>
       </c>
       <c r="X24" s="10">
-        <f t="shared" ref="X24" si="28">SUM(K24:N24)</f>
+        <f t="shared" ref="X24" si="26">SUM(K24:N24)</f>
         <v>82.515999999999991</v>
       </c>
       <c r="Y24" s="10">
-        <f t="shared" ref="Y24:Y26" si="29">SUM(O24:R24)</f>
-        <v>83.067999999999998</v>
+        <f t="shared" ref="Y24:Y26" si="27">SUM(O24:R24)</f>
+        <v>86.722000000000008</v>
       </c>
       <c r="Z24" s="3">
         <f>+Y24</f>
-        <v>83.067999999999998</v>
+        <v>86.722000000000008</v>
       </c>
       <c r="AA24" s="3">
         <f>+Z24</f>
-        <v>83.067999999999998</v>
+        <v>86.722000000000008</v>
       </c>
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.2">
@@ -2588,35 +2582,35 @@
         <v>38</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" ref="C25:J25" si="30">+C23+C24</f>
+        <f t="shared" ref="C25:J25" si="28">+C23+C24</f>
         <v>0</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>-120.37899999999995</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>-79.806000000000054</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>-61.483999999999952</v>
       </c>
       <c r="G25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>-51.759000000000086</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>-34.008999999999986</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>-25.662000000000006</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>-52.086000000000013</v>
       </c>
       <c r="K25" s="3">
@@ -2636,48 +2630,48 @@
         <v>-30.95635000000004</v>
       </c>
       <c r="O25" s="3">
-        <f t="shared" ref="O25:R25" si="31">+O23+O24</f>
-        <v>-24.025500000000019</v>
+        <f t="shared" ref="O25:R25" si="29">+O23+O24</f>
+        <v>-33.32399999999997</v>
       </c>
       <c r="P25" s="3">
-        <f t="shared" si="31"/>
-        <v>0.20620000000002747</v>
+        <f t="shared" si="29"/>
+        <v>-43.129999999999924</v>
       </c>
       <c r="Q25" s="3">
-        <f t="shared" si="31"/>
-        <v>18.790999999999944</v>
+        <f t="shared" si="29"/>
+        <v>36.025479999999973</v>
       </c>
       <c r="R25" s="3">
-        <f t="shared" si="31"/>
-        <v>24.251482499999899</v>
+        <f t="shared" si="29"/>
+        <v>41.485962499999928</v>
       </c>
       <c r="U25" s="3">
-        <f t="shared" ref="U25:AA25" si="32">+U23+U24</f>
+        <f t="shared" ref="U25:AA25" si="30">+U23+U24</f>
         <v>-302.88900000000001</v>
       </c>
       <c r="V25" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>-333.25400000000019</v>
       </c>
       <c r="W25" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>-163.51600000000019</v>
       </c>
       <c r="X25" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>-166.70934999999994</v>
       </c>
       <c r="Y25" s="3">
-        <f t="shared" si="32"/>
-        <v>19.22318249999968</v>
+        <f t="shared" si="30"/>
+        <v>1.0574425000000076</v>
       </c>
       <c r="Z25" s="3">
-        <f t="shared" si="32"/>
-        <v>302.86694162499998</v>
+        <f t="shared" si="30"/>
+        <v>326.73315662500022</v>
       </c>
       <c r="AA25" s="3">
-        <f t="shared" si="32"/>
-        <v>628.6768887062492</v>
+        <f t="shared" si="30"/>
+        <v>662.89841445625007</v>
       </c>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.2">
@@ -2718,11 +2712,11 @@
       <c r="N26" s="12">
         <v>0</v>
       </c>
-      <c r="O26" s="12">
-        <v>0</v>
-      </c>
-      <c r="P26" s="12">
-        <v>0</v>
+      <c r="O26" s="26">
+        <v>4.3019999999999996</v>
+      </c>
+      <c r="P26" s="26">
+        <v>3.9279999999999999</v>
       </c>
       <c r="Q26" s="12">
         <v>0</v>
@@ -2737,24 +2731,24 @@
         <v>12.144</v>
       </c>
       <c r="W26" s="3">
-        <f t="shared" ref="W26" si="33">SUM(G26:J26)</f>
+        <f t="shared" ref="W26" si="31">SUM(G26:J26)</f>
         <v>13.084000000000001</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" ref="X26" si="34">SUM(K26:N26)</f>
+        <f t="shared" ref="X26" si="32">SUM(K26:N26)</f>
         <v>9.1449999999999996</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>8.23</v>
       </c>
       <c r="Z26" s="3">
         <f>+Z25*0.1</f>
-        <v>30.286694162499998</v>
+        <v>32.673315662500023</v>
       </c>
       <c r="AA26" s="3">
         <f>+AA25*0.2</f>
-        <v>125.73537774124985</v>
+        <v>132.57968289125003</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.2">
@@ -2762,35 +2756,35 @@
         <v>8</v>
       </c>
       <c r="C27" s="3">
-        <f t="shared" ref="C27:J27" si="35">+C25-C26</f>
+        <f t="shared" ref="C27:J27" si="33">+C25-C26</f>
         <v>0</v>
       </c>
       <c r="D27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-123.42799999999995</v>
       </c>
       <c r="E27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-84.841000000000051</v>
       </c>
       <c r="F27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-64.397999999999954</v>
       </c>
       <c r="G27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-54.246000000000087</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-37.596999999999987</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-29.297000000000004</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>-55.460000000000015</v>
       </c>
       <c r="K27" s="3">
@@ -2810,48 +2804,48 @@
         <v>-30.95635000000004</v>
       </c>
       <c r="O27" s="3">
-        <f t="shared" ref="O27:R27" si="36">+O25-O26</f>
-        <v>-24.025500000000019</v>
+        <f t="shared" ref="O27:R27" si="34">+O25-O26</f>
+        <v>-37.625999999999969</v>
       </c>
       <c r="P27" s="3">
-        <f t="shared" si="36"/>
-        <v>0.20620000000002747</v>
+        <f t="shared" si="34"/>
+        <v>-47.057999999999922</v>
       </c>
       <c r="Q27" s="3">
-        <f t="shared" si="36"/>
-        <v>18.790999999999944</v>
+        <f t="shared" si="34"/>
+        <v>36.025479999999973</v>
       </c>
       <c r="R27" s="3">
-        <f t="shared" si="36"/>
-        <v>24.251482499999899</v>
+        <f t="shared" si="34"/>
+        <v>41.485962499999928</v>
       </c>
       <c r="U27" s="3">
-        <f t="shared" ref="U27:AA27" si="37">+U25-U26</f>
+        <f t="shared" ref="U27:AA27" si="35">+U25-U26</f>
         <v>-306.86599999999999</v>
       </c>
       <c r="V27" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>-345.3980000000002</v>
       </c>
       <c r="W27" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>-176.60000000000019</v>
       </c>
       <c r="X27" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>-175.85434999999995</v>
       </c>
       <c r="Y27" s="3">
-        <f t="shared" si="37"/>
-        <v>19.22318249999968</v>
+        <f t="shared" si="35"/>
+        <v>-7.1725574999999928</v>
       </c>
       <c r="Z27" s="3">
-        <f t="shared" si="37"/>
-        <v>272.58024746249998</v>
+        <f t="shared" si="35"/>
+        <v>294.05984096250018</v>
       </c>
       <c r="AA27" s="3">
-        <f t="shared" si="37"/>
-        <v>502.94151096499934</v>
+        <f t="shared" si="35"/>
+        <v>530.31873156500001</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.2">
@@ -2859,35 +2853,35 @@
         <v>40</v>
       </c>
       <c r="C28" s="7" t="e">
-        <f t="shared" ref="C28:J28" si="38">C27/C29</f>
+        <f t="shared" ref="C28:J28" si="36">C27/C29</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>-1.8062335280774275</v>
       </c>
       <c r="E28" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>-1.2310638914773968</v>
       </c>
       <c r="F28" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>-0.92625357140093434</v>
       </c>
       <c r="G28" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>-0.77298280464511981</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>-0.53047574476307036</v>
       </c>
       <c r="I28" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>-0.40940456377438567</v>
       </c>
       <c r="J28" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>-0.76655837267370075</v>
       </c>
       <c r="K28" s="7">
@@ -2907,48 +2901,48 @@
         <v>-0.41821267224919473</v>
       </c>
       <c r="O28" s="7">
-        <f t="shared" ref="O28:R28" si="39">O27/O29</f>
-        <v>-0.32457859395965682</v>
+        <f t="shared" ref="O28:R28" si="37">O27/O29</f>
+        <v>-0.46416997843915236</v>
       </c>
       <c r="P28" s="7">
-        <f t="shared" si="39"/>
-        <v>2.5456790123460182E-3</v>
+        <f t="shared" si="37"/>
+        <v>-0.58040405535410244</v>
       </c>
       <c r="Q28" s="7">
-        <f t="shared" si="39"/>
-        <v>0.23198765432098695</v>
+        <f t="shared" si="37"/>
+        <v>0.4443311379165738</v>
       </c>
       <c r="R28" s="7">
-        <f t="shared" si="39"/>
-        <v>0.29940101851851725</v>
+        <f t="shared" si="37"/>
+        <v>0.51167964799328947</v>
       </c>
       <c r="U28" s="7">
-        <f t="shared" ref="U28:AA28" si="40">U27/U29</f>
+        <f t="shared" ref="U28:AA28" si="38">U27/U29</f>
         <v>-4.7529676115582671</v>
       </c>
       <c r="V28" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>-5.0328824418661222</v>
       </c>
       <c r="W28" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>-2.478935809701309</v>
       </c>
       <c r="X28" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>-2.171041358024691</v>
       </c>
       <c r="Y28" s="7">
-        <f t="shared" si="40"/>
-        <v>0.2373232407407368</v>
+        <f t="shared" si="38"/>
+        <v>-8.85500925925925E-2</v>
       </c>
       <c r="Z28" s="7">
-        <f t="shared" si="40"/>
-        <v>3.3651882402777775</v>
+        <f t="shared" si="38"/>
+        <v>3.6303684069444464</v>
       </c>
       <c r="AA28" s="7">
-        <f t="shared" si="40"/>
-        <v>6.2091544563580161</v>
+        <f t="shared" si="38"/>
+        <v>6.5471448341358025</v>
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.2">
@@ -2991,19 +2985,18 @@
         <v>74.020593000000005</v>
       </c>
       <c r="O29" s="10">
-        <f>+N29</f>
-        <v>74.020593000000005</v>
+        <v>81.060822000000002</v>
       </c>
       <c r="P29" s="10">
-        <v>81</v>
+        <v>81.078000000000003</v>
       </c>
       <c r="Q29" s="10">
-        <f t="shared" ref="P29:R29" si="41">+P29</f>
-        <v>81</v>
+        <f t="shared" ref="Q29:R29" si="39">+P29</f>
+        <v>81.078000000000003</v>
       </c>
       <c r="R29" s="10">
-        <f t="shared" si="41"/>
-        <v>81</v>
+        <f t="shared" si="39"/>
+        <v>81.078000000000003</v>
       </c>
       <c r="U29" s="3">
         <v>64.563032000000007</v>
@@ -3037,71 +3030,71 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
-        <f t="shared" ref="H31:R31" si="42">H16/D16-1</f>
+        <f t="shared" ref="H31:R31" si="40">H16/D16-1</f>
         <v>0.39188825245014303</v>
       </c>
       <c r="I31" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>0.29769409000032976</v>
       </c>
       <c r="J31" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>0.26760805065981752</v>
       </c>
       <c r="K31" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>0.22341968067774531</v>
       </c>
       <c r="L31" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>0.12817166952578041</v>
       </c>
       <c r="M31" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>0.22275013974287305</v>
       </c>
       <c r="N31" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>0.13099942795009634</v>
       </c>
       <c r="O31" s="5">
-        <f t="shared" si="42"/>
-        <v>0.20738368389629813</v>
+        <f t="shared" si="40"/>
+        <v>0.21851203277691589</v>
       </c>
       <c r="P31" s="5">
-        <f t="shared" si="42"/>
-        <v>0.19219675847976103</v>
+        <f t="shared" si="40"/>
+        <v>0.23696060940078523</v>
       </c>
       <c r="Q31" s="5">
-        <f t="shared" si="42"/>
-        <v>0.12585596221959849</v>
+        <f t="shared" si="40"/>
+        <v>0.16628476977567885</v>
       </c>
       <c r="R31" s="5">
-        <f t="shared" si="42"/>
-        <v>0.20077220077220082</v>
+        <f t="shared" si="40"/>
+        <v>0.2420888030888031</v>
       </c>
       <c r="V31" s="19">
-        <f t="shared" ref="V31:AA31" si="43">+V16/U16-1</f>
+        <f t="shared" ref="V31:AA31" si="41">+V16/U16-1</f>
         <v>0.46951985735572488</v>
       </c>
       <c r="W31" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>0.31071539827419703</v>
       </c>
       <c r="X31" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>0.17411294400333688</v>
       </c>
       <c r="Y31" s="19">
-        <f t="shared" si="43"/>
-        <v>0.18013506777426613</v>
+        <f t="shared" si="41"/>
+        <v>0.21516463440862954</v>
       </c>
       <c r="Z31" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AA31" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>0.19999999999999996</v>
       </c>
     </row>
@@ -3110,91 +3103,91 @@
         <v>90</v>
       </c>
       <c r="D32" s="19">
-        <f t="shared" ref="D32:F32" si="44">+D18/D16</f>
+        <f t="shared" ref="D32:F32" si="42">+D18/D16</f>
         <v>0.69241178170734918</v>
       </c>
       <c r="E32" s="19">
+        <f t="shared" si="42"/>
+        <v>0.71928625596110563</v>
+      </c>
+      <c r="F32" s="19">
+        <f t="shared" si="42"/>
+        <v>0.75323266318306625</v>
+      </c>
+      <c r="G32" s="19">
+        <f t="shared" ref="G32:L32" si="43">+G18/G16</f>
+        <v>0.73539426523297491</v>
+      </c>
+      <c r="H32" s="19">
+        <f t="shared" si="43"/>
+        <v>0.75144115849557924</v>
+      </c>
+      <c r="I32" s="19">
+        <f t="shared" si="43"/>
+        <v>0.75271747917715703</v>
+      </c>
+      <c r="J32" s="19">
+        <f t="shared" si="43"/>
+        <v>0.74969323278064282</v>
+      </c>
+      <c r="K32" s="19">
+        <f t="shared" si="43"/>
+        <v>0.72767949289885281</v>
+      </c>
+      <c r="L32" s="19">
+        <f t="shared" si="43"/>
+        <v>0.73174945462227237</v>
+      </c>
+      <c r="M32" s="19">
+        <f t="shared" ref="M32:R32" si="44">+M18/M16</f>
+        <v>0.74435702479338839</v>
+      </c>
+      <c r="N32" s="19">
         <f t="shared" si="44"/>
-        <v>0.71928625596110563</v>
-      </c>
-      <c r="F32" s="19">
+        <v>0.74</v>
+      </c>
+      <c r="O32" s="19">
         <f t="shared" si="44"/>
-        <v>0.75323266318306625</v>
-      </c>
-      <c r="G32" s="19">
-        <f t="shared" ref="G32:L32" si="45">+G18/G16</f>
-        <v>0.73539426523297491</v>
-      </c>
-      <c r="H32" s="19">
+        <v>0.71213666682452548</v>
+      </c>
+      <c r="P32" s="19">
+        <f t="shared" si="44"/>
+        <v>0.71013287070385289</v>
+      </c>
+      <c r="Q32" s="19">
+        <f t="shared" si="44"/>
+        <v>0.74</v>
+      </c>
+      <c r="R32" s="19">
+        <f t="shared" si="44"/>
+        <v>0.74</v>
+      </c>
+      <c r="U32" s="19">
+        <f t="shared" ref="U32:AA32" si="45">+U18/U16</f>
+        <v>0.703024324144924</v>
+      </c>
+      <c r="V32" s="19">
         <f t="shared" si="45"/>
-        <v>0.75144115849557924</v>
-      </c>
-      <c r="I32" s="19">
+        <v>0.7279648609077598</v>
+      </c>
+      <c r="W32" s="19">
         <f t="shared" si="45"/>
-        <v>0.75271747917715703</v>
-      </c>
-      <c r="J32" s="19">
+        <v>0.74778239714416594</v>
+      </c>
+      <c r="X32" s="19">
         <f t="shared" si="45"/>
-        <v>0.74969323278064282</v>
-      </c>
-      <c r="K32" s="19">
+        <v>0.73636177313775752</v>
+      </c>
+      <c r="Y32" s="19">
         <f t="shared" si="45"/>
-        <v>0.72767949289885281</v>
-      </c>
-      <c r="L32" s="19">
+        <v>0.72627329440867561</v>
+      </c>
+      <c r="Z32" s="19">
         <f t="shared" si="45"/>
-        <v>0.73174945462227237</v>
-      </c>
-      <c r="M32" s="19">
-        <f t="shared" ref="M32:R32" si="46">+M18/M16</f>
-        <v>0.74435702479338839</v>
-      </c>
-      <c r="N32" s="19">
-        <f t="shared" si="46"/>
-        <v>0.74</v>
-      </c>
-      <c r="O32" s="19">
-        <f t="shared" si="46"/>
-        <v>0.74</v>
-      </c>
-      <c r="P32" s="19">
-        <f t="shared" si="46"/>
-        <v>0.74</v>
-      </c>
-      <c r="Q32" s="19">
-        <f t="shared" si="46"/>
-        <v>0.74</v>
-      </c>
-      <c r="R32" s="19">
-        <f t="shared" si="46"/>
-        <v>0.74</v>
-      </c>
-      <c r="U32" s="19">
-        <f t="shared" ref="U32:AA32" si="47">+U18/U16</f>
-        <v>0.703024324144924</v>
-      </c>
-      <c r="V32" s="19">
-        <f t="shared" si="47"/>
-        <v>0.7279648609077598</v>
-      </c>
-      <c r="W32" s="19">
-        <f t="shared" si="47"/>
-        <v>0.74778239714416594</v>
-      </c>
-      <c r="X32" s="19">
-        <f t="shared" si="47"/>
-        <v>0.73636177313775752</v>
-      </c>
-      <c r="Y32" s="19">
-        <f t="shared" si="47"/>
-        <v>0.74</v>
-      </c>
-      <c r="Z32" s="19">
-        <f t="shared" si="47"/>
         <v>0.75</v>
       </c>
       <c r="AA32" s="19">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0.75</v>
       </c>
     </row>
@@ -3351,7 +3344,7 @@
       </c>
       <c r="AC39" s="21">
         <f>NPV(AC38,U16:BY16)</f>
-        <v>47391.850417467293</v>
+        <v>48669.102445567631</v>
       </c>
     </row>
     <row r="40" spans="2:33" x14ac:dyDescent="0.2">
@@ -3414,7 +3407,7 @@
       </c>
       <c r="AC41" s="21">
         <f>AC39/AC40</f>
-        <v>585.08457305515174</v>
+        <v>600.85311661194601</v>
       </c>
     </row>
     <row r="42" spans="2:33" ht="15.75" x14ac:dyDescent="0.25">
@@ -3444,7 +3437,7 @@
       </c>
       <c r="AC42" s="23">
         <f>(AC41-Main!J2)/Main!J2</f>
-        <v>0.84884210660162984</v>
+        <v>0.89867002658138795</v>
       </c>
     </row>
     <row r="43" spans="2:33" x14ac:dyDescent="0.2">
@@ -3499,14 +3492,14 @@
     </row>
     <row r="45" spans="2:33" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L45" s="3"/>
-      <c r="AB45" s="24" t="s">
+      <c r="AB45" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="AC45" s="24"/>
-      <c r="AD45" s="24"/>
-      <c r="AE45" s="25"/>
-      <c r="AF45" s="25"/>
-      <c r="AG45" s="25"/>
+      <c r="AC45" s="25"/>
+      <c r="AD45" s="25"/>
+      <c r="AE45" s="24"/>
+      <c r="AF45" s="24"/>
+      <c r="AG45" s="24"/>
     </row>
     <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
@@ -3530,12 +3523,12 @@
       <c r="M46" s="10">
         <v>11.444000000000001</v>
       </c>
-      <c r="AB46" s="25"/>
-      <c r="AC46" s="25"/>
-      <c r="AD46" s="25"/>
-      <c r="AE46" s="25"/>
-      <c r="AF46" s="25"/>
-      <c r="AG46" s="25"/>
+      <c r="AB46" s="24"/>
+      <c r="AC46" s="24"/>
+      <c r="AD46" s="24"/>
+      <c r="AE46" s="24"/>
+      <c r="AF46" s="24"/>
+      <c r="AG46" s="24"/>
     </row>
     <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -3559,12 +3552,12 @@
       <c r="M47" s="10">
         <v>120.598</v>
       </c>
-      <c r="AB47" s="25"/>
-      <c r="AC47" s="25"/>
-      <c r="AD47" s="25"/>
-      <c r="AE47" s="25"/>
-      <c r="AF47" s="25"/>
-      <c r="AG47" s="25"/>
+      <c r="AB47" s="24"/>
+      <c r="AC47" s="24"/>
+      <c r="AD47" s="24"/>
+      <c r="AE47" s="24"/>
+      <c r="AF47" s="24"/>
+      <c r="AG47" s="24"/>
     </row>
     <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -3592,12 +3585,12 @@
         <f>10.787+27.639</f>
         <v>38.426000000000002</v>
       </c>
-      <c r="AB48" s="25"/>
-      <c r="AC48" s="25"/>
-      <c r="AD48" s="25"/>
-      <c r="AE48" s="25"/>
-      <c r="AF48" s="25"/>
-      <c r="AG48" s="25"/>
+      <c r="AB48" s="24"/>
+      <c r="AC48" s="24"/>
+      <c r="AD48" s="24"/>
+      <c r="AE48" s="24"/>
+      <c r="AF48" s="24"/>
+      <c r="AG48" s="24"/>
     </row>
     <row r="49" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
@@ -3791,15 +3784,15 @@
         <v>-9.7760000000000336</v>
       </c>
       <c r="U57" s="10">
-        <f t="shared" ref="U57:W57" si="48">+U27</f>
+        <f t="shared" ref="U57:W57" si="46">+U27</f>
         <v>-306.86599999999999</v>
       </c>
       <c r="V57" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>-345.3980000000002</v>
       </c>
       <c r="W57" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>-176.60000000000019</v>
       </c>
       <c r="X57" s="10">
@@ -3808,7 +3801,7 @@
       </c>
       <c r="Y57" s="10">
         <f>+Y27</f>
-        <v>19.22318249999968</v>
+        <v>-7.1725574999999928</v>
       </c>
     </row>
     <row r="58" spans="2:25" x14ac:dyDescent="0.2">
@@ -4322,15 +4315,15 @@
         <v>35.457000000000001</v>
       </c>
       <c r="U85" s="3">
-        <f t="shared" ref="U85:W85" si="49">+U65+U67</f>
+        <f t="shared" ref="U85:W85" si="47">+U65+U67</f>
         <v>-1.0920000000000236</v>
       </c>
       <c r="V85" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>-20.21399999999997</v>
       </c>
       <c r="W85" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>113.405</v>
       </c>
     </row>

--- a/MDB.xlsx
+++ b/MDB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7214B778-82C9-4B2A-96B2-A6BE8B040105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B1156D-CBD9-4F81-B6A0-BABE0A336BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14235" yWindow="90" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{9A102858-C73E-5D48-A2CD-E1A822063168}"/>
+    <workbookView xWindow="-15" yWindow="90" windowWidth="14370" windowHeight="20805" xr2:uid="{9A102858-C73E-5D48-A2CD-E1A822063168}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -455,9 +455,9 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
-    <numFmt numFmtId="171" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -517,12 +517,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -601,18 +595,15 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -634,6 +625,9 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1114,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="15">
-        <v>316.45999999999998</v>
+        <v>359.82</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.2">
@@ -1138,7 +1132,7 @@
       </c>
       <c r="J4" s="16">
         <f>+J2*J3</f>
-        <v>25747.185599999997</v>
+        <v>29274.9552</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.2">
@@ -1171,7 +1165,7 @@
       </c>
       <c r="J7" s="16">
         <f>+J4-J5+J6</f>
-        <v>24570.185599999997</v>
+        <v>28097.9552</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.2">
@@ -1215,7 +1209,7 @@
     <col min="3" max="7" width="10.875" style="1"/>
     <col min="8" max="12" width="9.625" style="1" customWidth="1"/>
     <col min="13" max="16" width="9.625" style="12" customWidth="1"/>
-    <col min="17" max="18" width="9.625" style="32" customWidth="1"/>
+    <col min="17" max="18" width="9.625" style="31" customWidth="1"/>
     <col min="19" max="21" width="10.875" style="1"/>
     <col min="22" max="22" width="11.125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.625" style="1" bestFit="1" customWidth="1"/>
@@ -1279,11 +1273,11 @@
         <f>+L2+365</f>
         <v>45869</v>
       </c>
-      <c r="Q2" s="33">
+      <c r="Q2" s="32">
         <f>+M2+365</f>
         <v>45961</v>
       </c>
-      <c r="R2" s="33">
+      <c r="R2" s="32">
         <f>+N2+365</f>
         <v>46053</v>
       </c>
@@ -1349,10 +1343,10 @@
       <c r="P3" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="Q3" s="32" t="s">
+      <c r="Q3" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="R3" s="32" t="s">
+      <c r="R3" s="31" t="s">
         <v>89</v>
       </c>
       <c r="U3" s="12" t="s">
@@ -1565,15 +1559,15 @@
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
-      <c r="V12" s="40">
+      <c r="V12" s="39">
         <f>(V13-U13)/U13</f>
         <v>0.65320983952519029</v>
       </c>
-      <c r="W12" s="40">
+      <c r="W12" s="39">
         <f>(W13-V13)/V13</f>
         <v>0.37313041723963508</v>
       </c>
-      <c r="X12" s="40">
+      <c r="X12" s="39">
         <f>(X13-W13)/W13</f>
         <v>0.26442888803027864</v>
       </c>
@@ -1595,75 +1589,75 @@
       <c r="K13" s="11">
         <v>313.85500000000002</v>
       </c>
-      <c r="U13" s="29">
+      <c r="U13" s="28">
         <f>0.56*U18</f>
         <v>489.31792000000007</v>
       </c>
-      <c r="V13" s="29">
+      <c r="V13" s="28">
         <f>0.63*V18</f>
         <v>808.9452</v>
       </c>
-      <c r="W13" s="29">
+      <c r="W13" s="28">
         <f>0.66*W18</f>
         <v>1110.7872600000001</v>
       </c>
-      <c r="X13" s="30">
+      <c r="X13" s="29">
         <f>0.7*X18</f>
         <v>1404.5115000000001</v>
       </c>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="29"/>
-      <c r="AA13" s="29"/>
-      <c r="AB13" s="29"/>
-      <c r="AC13" s="29"/>
-      <c r="AD13" s="29"/>
-      <c r="AE13" s="29"/>
-      <c r="AF13" s="29"/>
-      <c r="AG13" s="29"/>
-      <c r="AH13" s="29"/>
-      <c r="AI13" s="29"/>
-      <c r="AJ13" s="29"/>
-      <c r="AK13" s="29"/>
-      <c r="AL13" s="29"/>
-      <c r="AM13" s="29"/>
-      <c r="AN13" s="29"/>
-      <c r="AO13" s="29"/>
-      <c r="AP13" s="29"/>
-      <c r="AQ13" s="29"/>
-      <c r="AR13" s="29"/>
-      <c r="AS13" s="29"/>
-      <c r="AT13" s="29"/>
-      <c r="AU13" s="29"/>
-      <c r="AV13" s="29"/>
-      <c r="AW13" s="29"/>
-      <c r="AX13" s="29"/>
-      <c r="AY13" s="29"/>
-      <c r="AZ13" s="29"/>
-      <c r="BA13" s="29"/>
-      <c r="BB13" s="29"/>
-      <c r="BC13" s="29"/>
-      <c r="BD13" s="29"/>
-      <c r="BE13" s="29"/>
-      <c r="BF13" s="29"/>
-      <c r="BG13" s="29"/>
-      <c r="BH13" s="29"/>
-      <c r="BI13" s="29"/>
-      <c r="BJ13" s="29"/>
-      <c r="BK13" s="29"/>
-      <c r="BL13" s="29"/>
-      <c r="BM13" s="29"/>
-      <c r="BN13" s="29"/>
-      <c r="BO13" s="29"/>
-      <c r="BP13" s="29"/>
-      <c r="BQ13" s="29"/>
-      <c r="BR13" s="29"/>
-      <c r="BS13" s="29"/>
-      <c r="BT13" s="29"/>
-      <c r="BU13" s="29"/>
-      <c r="BV13" s="29"/>
-      <c r="BW13" s="29"/>
-      <c r="BX13" s="29"/>
-      <c r="BY13" s="29"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="28"/>
+      <c r="AA13" s="28"/>
+      <c r="AB13" s="28"/>
+      <c r="AC13" s="28"/>
+      <c r="AD13" s="28"/>
+      <c r="AE13" s="28"/>
+      <c r="AF13" s="28"/>
+      <c r="AG13" s="28"/>
+      <c r="AH13" s="28"/>
+      <c r="AI13" s="28"/>
+      <c r="AJ13" s="28"/>
+      <c r="AK13" s="28"/>
+      <c r="AL13" s="28"/>
+      <c r="AM13" s="28"/>
+      <c r="AN13" s="28"/>
+      <c r="AO13" s="28"/>
+      <c r="AP13" s="28"/>
+      <c r="AQ13" s="28"/>
+      <c r="AR13" s="28"/>
+      <c r="AS13" s="28"/>
+      <c r="AT13" s="28"/>
+      <c r="AU13" s="28"/>
+      <c r="AV13" s="28"/>
+      <c r="AW13" s="28"/>
+      <c r="AX13" s="28"/>
+      <c r="AY13" s="28"/>
+      <c r="AZ13" s="28"/>
+      <c r="BA13" s="28"/>
+      <c r="BB13" s="28"/>
+      <c r="BC13" s="28"/>
+      <c r="BD13" s="28"/>
+      <c r="BE13" s="28"/>
+      <c r="BF13" s="28"/>
+      <c r="BG13" s="28"/>
+      <c r="BH13" s="28"/>
+      <c r="BI13" s="28"/>
+      <c r="BJ13" s="28"/>
+      <c r="BK13" s="28"/>
+      <c r="BL13" s="28"/>
+      <c r="BM13" s="28"/>
+      <c r="BN13" s="28"/>
+      <c r="BO13" s="28"/>
+      <c r="BP13" s="28"/>
+      <c r="BQ13" s="28"/>
+      <c r="BR13" s="28"/>
+      <c r="BS13" s="28"/>
+      <c r="BT13" s="28"/>
+      <c r="BU13" s="28"/>
+      <c r="BV13" s="28"/>
+      <c r="BW13" s="28"/>
+      <c r="BX13" s="28"/>
+      <c r="BY13" s="28"/>
     </row>
     <row r="14" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -1678,69 +1672,69 @@
       <c r="I14" s="11"/>
       <c r="J14" s="10"/>
       <c r="K14" s="11"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="40">
+      <c r="U14" s="28"/>
+      <c r="V14" s="28"/>
+      <c r="W14" s="39">
         <f>(W15-V15)/V15</f>
         <v>0.21709286982604004</v>
       </c>
-      <c r="X14" s="40">
+      <c r="X14" s="39">
         <f>(X15-W15)/W15</f>
         <v>5.4617061554924871E-2</v>
       </c>
-      <c r="Y14" s="31"/>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="29"/>
-      <c r="AD14" s="29"/>
-      <c r="AE14" s="29"/>
-      <c r="AF14" s="29"/>
-      <c r="AG14" s="29"/>
-      <c r="AH14" s="29"/>
-      <c r="AI14" s="29"/>
-      <c r="AJ14" s="29"/>
-      <c r="AK14" s="29"/>
-      <c r="AL14" s="29"/>
-      <c r="AM14" s="29"/>
-      <c r="AN14" s="29"/>
-      <c r="AO14" s="29"/>
-      <c r="AP14" s="29"/>
-      <c r="AQ14" s="29"/>
-      <c r="AR14" s="29"/>
-      <c r="AS14" s="29"/>
-      <c r="AT14" s="29"/>
-      <c r="AU14" s="29"/>
-      <c r="AV14" s="29"/>
-      <c r="AW14" s="29"/>
-      <c r="AX14" s="29"/>
-      <c r="AY14" s="29"/>
-      <c r="AZ14" s="29"/>
-      <c r="BA14" s="29"/>
-      <c r="BB14" s="29"/>
-      <c r="BC14" s="29"/>
-      <c r="BD14" s="29"/>
-      <c r="BE14" s="29"/>
-      <c r="BF14" s="29"/>
-      <c r="BG14" s="29"/>
-      <c r="BH14" s="29"/>
-      <c r="BI14" s="29"/>
-      <c r="BJ14" s="29"/>
-      <c r="BK14" s="29"/>
-      <c r="BL14" s="29"/>
-      <c r="BM14" s="29"/>
-      <c r="BN14" s="29"/>
-      <c r="BO14" s="29"/>
-      <c r="BP14" s="29"/>
-      <c r="BQ14" s="29"/>
-      <c r="BR14" s="29"/>
-      <c r="BS14" s="29"/>
-      <c r="BT14" s="29"/>
-      <c r="BU14" s="29"/>
-      <c r="BV14" s="29"/>
-      <c r="BW14" s="29"/>
-      <c r="BX14" s="29"/>
-      <c r="BY14" s="29"/>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="28"/>
+      <c r="AA14" s="28"/>
+      <c r="AB14" s="28"/>
+      <c r="AC14" s="28"/>
+      <c r="AD14" s="28"/>
+      <c r="AE14" s="28"/>
+      <c r="AF14" s="28"/>
+      <c r="AG14" s="28"/>
+      <c r="AH14" s="28"/>
+      <c r="AI14" s="28"/>
+      <c r="AJ14" s="28"/>
+      <c r="AK14" s="28"/>
+      <c r="AL14" s="28"/>
+      <c r="AM14" s="28"/>
+      <c r="AN14" s="28"/>
+      <c r="AO14" s="28"/>
+      <c r="AP14" s="28"/>
+      <c r="AQ14" s="28"/>
+      <c r="AR14" s="28"/>
+      <c r="AS14" s="28"/>
+      <c r="AT14" s="28"/>
+      <c r="AU14" s="28"/>
+      <c r="AV14" s="28"/>
+      <c r="AW14" s="28"/>
+      <c r="AX14" s="28"/>
+      <c r="AY14" s="28"/>
+      <c r="AZ14" s="28"/>
+      <c r="BA14" s="28"/>
+      <c r="BB14" s="28"/>
+      <c r="BC14" s="28"/>
+      <c r="BD14" s="28"/>
+      <c r="BE14" s="28"/>
+      <c r="BF14" s="28"/>
+      <c r="BG14" s="28"/>
+      <c r="BH14" s="28"/>
+      <c r="BI14" s="28"/>
+      <c r="BJ14" s="28"/>
+      <c r="BK14" s="28"/>
+      <c r="BL14" s="28"/>
+      <c r="BM14" s="28"/>
+      <c r="BN14" s="28"/>
+      <c r="BO14" s="28"/>
+      <c r="BP14" s="28"/>
+      <c r="BQ14" s="28"/>
+      <c r="BR14" s="28"/>
+      <c r="BS14" s="28"/>
+      <c r="BT14" s="28"/>
+      <c r="BU14" s="28"/>
+      <c r="BV14" s="28"/>
+      <c r="BW14" s="28"/>
+      <c r="BX14" s="28"/>
+      <c r="BY14" s="28"/>
     </row>
     <row r="15" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
@@ -1759,72 +1753,72 @@
       <c r="K15" s="11">
         <v>123.041</v>
       </c>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29">
+      <c r="U15" s="28"/>
+      <c r="V15" s="28">
         <f>0.28*V18</f>
         <v>359.53120000000001</v>
       </c>
-      <c r="W15" s="29">
+      <c r="W15" s="28">
         <f>0.26*W18</f>
         <v>437.58285999999998</v>
       </c>
-      <c r="X15" s="31">
+      <c r="X15" s="30">
         <f>0.23*X18</f>
         <v>461.48235000000005</v>
       </c>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="29"/>
-      <c r="AA15" s="29"/>
-      <c r="AB15" s="29"/>
-      <c r="AC15" s="29"/>
-      <c r="AD15" s="29"/>
-      <c r="AE15" s="29"/>
-      <c r="AF15" s="29"/>
-      <c r="AG15" s="29"/>
-      <c r="AH15" s="29"/>
-      <c r="AI15" s="29"/>
-      <c r="AJ15" s="29"/>
-      <c r="AK15" s="29"/>
-      <c r="AL15" s="29"/>
-      <c r="AM15" s="29"/>
-      <c r="AN15" s="29"/>
-      <c r="AO15" s="29"/>
-      <c r="AP15" s="29"/>
-      <c r="AQ15" s="29"/>
-      <c r="AR15" s="29"/>
-      <c r="AS15" s="29"/>
-      <c r="AT15" s="29"/>
-      <c r="AU15" s="29"/>
-      <c r="AV15" s="29"/>
-      <c r="AW15" s="29"/>
-      <c r="AX15" s="29"/>
-      <c r="AY15" s="29"/>
-      <c r="AZ15" s="29"/>
-      <c r="BA15" s="29"/>
-      <c r="BB15" s="29"/>
-      <c r="BC15" s="29"/>
-      <c r="BD15" s="29"/>
-      <c r="BE15" s="29"/>
-      <c r="BF15" s="29"/>
-      <c r="BG15" s="29"/>
-      <c r="BH15" s="29"/>
-      <c r="BI15" s="29"/>
-      <c r="BJ15" s="29"/>
-      <c r="BK15" s="29"/>
-      <c r="BL15" s="29"/>
-      <c r="BM15" s="29"/>
-      <c r="BN15" s="29"/>
-      <c r="BO15" s="29"/>
-      <c r="BP15" s="29"/>
-      <c r="BQ15" s="29"/>
-      <c r="BR15" s="29"/>
-      <c r="BS15" s="29"/>
-      <c r="BT15" s="29"/>
-      <c r="BU15" s="29"/>
-      <c r="BV15" s="29"/>
-      <c r="BW15" s="29"/>
-      <c r="BX15" s="29"/>
-      <c r="BY15" s="29"/>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="28"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="28"/>
+      <c r="AC15" s="28"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="28"/>
+      <c r="AH15" s="28"/>
+      <c r="AI15" s="28"/>
+      <c r="AJ15" s="28"/>
+      <c r="AK15" s="28"/>
+      <c r="AL15" s="28"/>
+      <c r="AM15" s="28"/>
+      <c r="AN15" s="28"/>
+      <c r="AO15" s="28"/>
+      <c r="AP15" s="28"/>
+      <c r="AQ15" s="28"/>
+      <c r="AR15" s="28"/>
+      <c r="AS15" s="28"/>
+      <c r="AT15" s="28"/>
+      <c r="AU15" s="28"/>
+      <c r="AV15" s="28"/>
+      <c r="AW15" s="28"/>
+      <c r="AX15" s="28"/>
+      <c r="AY15" s="28"/>
+      <c r="AZ15" s="28"/>
+      <c r="BA15" s="28"/>
+      <c r="BB15" s="28"/>
+      <c r="BC15" s="28"/>
+      <c r="BD15" s="28"/>
+      <c r="BE15" s="28"/>
+      <c r="BF15" s="28"/>
+      <c r="BG15" s="28"/>
+      <c r="BH15" s="28"/>
+      <c r="BI15" s="28"/>
+      <c r="BJ15" s="28"/>
+      <c r="BK15" s="28"/>
+      <c r="BL15" s="28"/>
+      <c r="BM15" s="28"/>
+      <c r="BN15" s="28"/>
+      <c r="BO15" s="28"/>
+      <c r="BP15" s="28"/>
+      <c r="BQ15" s="28"/>
+      <c r="BR15" s="28"/>
+      <c r="BS15" s="28"/>
+      <c r="BT15" s="28"/>
+      <c r="BU15" s="28"/>
+      <c r="BV15" s="28"/>
+      <c r="BW15" s="28"/>
+      <c r="BX15" s="28"/>
+      <c r="BY15" s="28"/>
     </row>
     <row r="16" spans="1:77" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
@@ -1865,71 +1859,71 @@
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29">
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28">
         <v>1234.1220000000001</v>
       </c>
-      <c r="W16" s="29">
+      <c r="W16" s="28">
         <v>1627.326</v>
       </c>
-      <c r="X16" s="31">
+      <c r="X16" s="30">
         <v>1943.864</v>
       </c>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="29"/>
-      <c r="AA16" s="29"/>
-      <c r="AB16" s="29"/>
-      <c r="AC16" s="29"/>
-      <c r="AD16" s="29"/>
-      <c r="AE16" s="29"/>
-      <c r="AF16" s="29"/>
-      <c r="AG16" s="29"/>
-      <c r="AH16" s="29"/>
-      <c r="AI16" s="29"/>
-      <c r="AJ16" s="29"/>
-      <c r="AK16" s="29"/>
-      <c r="AL16" s="29"/>
-      <c r="AM16" s="29"/>
-      <c r="AN16" s="29"/>
-      <c r="AO16" s="29"/>
-      <c r="AP16" s="29"/>
-      <c r="AQ16" s="29"/>
-      <c r="AR16" s="29"/>
-      <c r="AS16" s="29"/>
-      <c r="AT16" s="29"/>
-      <c r="AU16" s="29"/>
-      <c r="AV16" s="29"/>
-      <c r="AW16" s="29"/>
-      <c r="AX16" s="29"/>
-      <c r="AY16" s="29"/>
-      <c r="AZ16" s="29"/>
-      <c r="BA16" s="29"/>
-      <c r="BB16" s="29"/>
-      <c r="BC16" s="29"/>
-      <c r="BD16" s="29"/>
-      <c r="BE16" s="29"/>
-      <c r="BF16" s="29"/>
-      <c r="BG16" s="29"/>
-      <c r="BH16" s="29"/>
-      <c r="BI16" s="29"/>
-      <c r="BJ16" s="29"/>
-      <c r="BK16" s="29"/>
-      <c r="BL16" s="29"/>
-      <c r="BM16" s="29"/>
-      <c r="BN16" s="29"/>
-      <c r="BO16" s="29"/>
-      <c r="BP16" s="29"/>
-      <c r="BQ16" s="29"/>
-      <c r="BR16" s="29"/>
-      <c r="BS16" s="29"/>
-      <c r="BT16" s="29"/>
-      <c r="BU16" s="29"/>
-      <c r="BV16" s="29"/>
-      <c r="BW16" s="29"/>
-      <c r="BX16" s="29"/>
-      <c r="BY16" s="29"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="28"/>
+      <c r="AA16" s="28"/>
+      <c r="AB16" s="28"/>
+      <c r="AC16" s="28"/>
+      <c r="AD16" s="28"/>
+      <c r="AE16" s="28"/>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="28"/>
+      <c r="AH16" s="28"/>
+      <c r="AI16" s="28"/>
+      <c r="AJ16" s="28"/>
+      <c r="AK16" s="28"/>
+      <c r="AL16" s="28"/>
+      <c r="AM16" s="28"/>
+      <c r="AN16" s="28"/>
+      <c r="AO16" s="28"/>
+      <c r="AP16" s="28"/>
+      <c r="AQ16" s="28"/>
+      <c r="AR16" s="28"/>
+      <c r="AS16" s="28"/>
+      <c r="AT16" s="28"/>
+      <c r="AU16" s="28"/>
+      <c r="AV16" s="28"/>
+      <c r="AW16" s="28"/>
+      <c r="AX16" s="28"/>
+      <c r="AY16" s="28"/>
+      <c r="AZ16" s="28"/>
+      <c r="BA16" s="28"/>
+      <c r="BB16" s="28"/>
+      <c r="BC16" s="28"/>
+      <c r="BD16" s="28"/>
+      <c r="BE16" s="28"/>
+      <c r="BF16" s="28"/>
+      <c r="BG16" s="28"/>
+      <c r="BH16" s="28"/>
+      <c r="BI16" s="28"/>
+      <c r="BJ16" s="28"/>
+      <c r="BK16" s="28"/>
+      <c r="BL16" s="28"/>
+      <c r="BM16" s="28"/>
+      <c r="BN16" s="28"/>
+      <c r="BO16" s="28"/>
+      <c r="BP16" s="28"/>
+      <c r="BQ16" s="28"/>
+      <c r="BR16" s="28"/>
+      <c r="BS16" s="28"/>
+      <c r="BT16" s="28"/>
+      <c r="BU16" s="28"/>
+      <c r="BV16" s="28"/>
+      <c r="BW16" s="28"/>
+      <c r="BX16" s="28"/>
+      <c r="BY16" s="28"/>
     </row>
     <row r="17" spans="2:77" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
@@ -1969,106 +1963,106 @@
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="U17" s="29"/>
-      <c r="V17" s="29">
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="U17" s="28"/>
+      <c r="V17" s="28">
         <v>48.917999999999999</v>
       </c>
-      <c r="W17" s="29">
+      <c r="W17" s="28">
         <v>55.685000000000002</v>
       </c>
-      <c r="X17" s="31">
+      <c r="X17" s="30">
         <v>62.579000000000001</v>
       </c>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="29"/>
-      <c r="AA17" s="29"/>
-      <c r="AB17" s="29"/>
-      <c r="AC17" s="29"/>
-      <c r="AD17" s="29"/>
-      <c r="AE17" s="29"/>
-      <c r="AF17" s="29"/>
-      <c r="AG17" s="29"/>
-      <c r="AH17" s="29"/>
-      <c r="AI17" s="29"/>
-      <c r="AJ17" s="29"/>
-      <c r="AK17" s="29"/>
-      <c r="AL17" s="29"/>
-      <c r="AM17" s="29"/>
-      <c r="AN17" s="29"/>
-      <c r="AO17" s="29"/>
-      <c r="AP17" s="29"/>
-      <c r="AQ17" s="29"/>
-      <c r="AR17" s="29"/>
-      <c r="AS17" s="29"/>
-      <c r="AT17" s="29"/>
-      <c r="AU17" s="29"/>
-      <c r="AV17" s="29"/>
-      <c r="AW17" s="29"/>
-      <c r="AX17" s="29"/>
-      <c r="AY17" s="29"/>
-      <c r="AZ17" s="29"/>
-      <c r="BA17" s="29"/>
-      <c r="BB17" s="29"/>
-      <c r="BC17" s="29"/>
-      <c r="BD17" s="29"/>
-      <c r="BE17" s="29"/>
-      <c r="BF17" s="29"/>
-      <c r="BG17" s="29"/>
-      <c r="BH17" s="29"/>
-      <c r="BI17" s="29"/>
-      <c r="BJ17" s="29"/>
-      <c r="BK17" s="29"/>
-      <c r="BL17" s="29"/>
-      <c r="BM17" s="29"/>
-      <c r="BN17" s="29"/>
-      <c r="BO17" s="29"/>
-      <c r="BP17" s="29"/>
-      <c r="BQ17" s="29"/>
-      <c r="BR17" s="29"/>
-      <c r="BS17" s="29"/>
-      <c r="BT17" s="29"/>
-      <c r="BU17" s="29"/>
-      <c r="BV17" s="29"/>
-      <c r="BW17" s="29"/>
-      <c r="BX17" s="29"/>
-      <c r="BY17" s="29"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="28"/>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="28"/>
+      <c r="AC17" s="28"/>
+      <c r="AD17" s="28"/>
+      <c r="AE17" s="28"/>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="28"/>
+      <c r="AH17" s="28"/>
+      <c r="AI17" s="28"/>
+      <c r="AJ17" s="28"/>
+      <c r="AK17" s="28"/>
+      <c r="AL17" s="28"/>
+      <c r="AM17" s="28"/>
+      <c r="AN17" s="28"/>
+      <c r="AO17" s="28"/>
+      <c r="AP17" s="28"/>
+      <c r="AQ17" s="28"/>
+      <c r="AR17" s="28"/>
+      <c r="AS17" s="28"/>
+      <c r="AT17" s="28"/>
+      <c r="AU17" s="28"/>
+      <c r="AV17" s="28"/>
+      <c r="AW17" s="28"/>
+      <c r="AX17" s="28"/>
+      <c r="AY17" s="28"/>
+      <c r="AZ17" s="28"/>
+      <c r="BA17" s="28"/>
+      <c r="BB17" s="28"/>
+      <c r="BC17" s="28"/>
+      <c r="BD17" s="28"/>
+      <c r="BE17" s="28"/>
+      <c r="BF17" s="28"/>
+      <c r="BG17" s="28"/>
+      <c r="BH17" s="28"/>
+      <c r="BI17" s="28"/>
+      <c r="BJ17" s="28"/>
+      <c r="BK17" s="28"/>
+      <c r="BL17" s="28"/>
+      <c r="BM17" s="28"/>
+      <c r="BN17" s="28"/>
+      <c r="BO17" s="28"/>
+      <c r="BP17" s="28"/>
+      <c r="BQ17" s="28"/>
+      <c r="BR17" s="28"/>
+      <c r="BS17" s="28"/>
+      <c r="BT17" s="28"/>
+      <c r="BU17" s="28"/>
+      <c r="BV17" s="28"/>
+      <c r="BW17" s="28"/>
+      <c r="BX17" s="28"/>
+      <c r="BY17" s="28"/>
     </row>
     <row r="18" spans="2:77" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="4">
-        <f>+D16+D17</f>
+        <f t="shared" ref="D18:K18" si="0">+D16+D17</f>
         <v>304.47200000000004</v>
       </c>
       <c r="E18" s="4">
-        <f>+E16+E17</f>
+        <f t="shared" si="0"/>
         <v>333.62099999999998</v>
       </c>
       <c r="F18" s="4">
-        <f>+F16+F17</f>
+        <f t="shared" si="0"/>
         <v>361.31200000000001</v>
       </c>
       <c r="G18" s="4">
-        <f>+G16+G17</f>
+        <f t="shared" si="0"/>
         <v>368.28</v>
       </c>
       <c r="H18" s="4">
-        <f>+H16+H17</f>
+        <f t="shared" si="0"/>
         <v>423.791</v>
       </c>
       <c r="I18" s="4">
-        <f>+I16+I17</f>
+        <f t="shared" si="0"/>
         <v>432.93799999999999</v>
       </c>
       <c r="J18" s="4">
-        <f>+J16+J17</f>
+        <f t="shared" si="0"/>
         <v>458.00200000000001</v>
       </c>
       <c r="K18" s="4">
-        <f>+K16+K17</f>
+        <f t="shared" si="0"/>
         <v>450.56100000000004</v>
       </c>
       <c r="L18" s="4">
@@ -2088,10 +2082,10 @@
       <c r="P18" s="4">
         <v>591.40200000000004</v>
       </c>
-      <c r="Q18" s="35">
+      <c r="Q18" s="34">
         <v>632</v>
       </c>
-      <c r="R18" s="35">
+      <c r="R18" s="34">
         <f>+Q18+26</f>
         <v>658</v>
       </c>
@@ -2118,31 +2112,31 @@
         <v>2916.4992000000002</v>
       </c>
       <c r="AA18" s="4">
-        <f t="shared" ref="AA18:AG18" si="0">+Z18*(1+$AC$42)</f>
+        <f t="shared" ref="AA18:AG18" si="1">+Z18*(1+$AC$42)</f>
         <v>3499.7990400000003</v>
       </c>
       <c r="AB18" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4199.7588480000004</v>
       </c>
       <c r="AC18" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5039.7106176000007</v>
       </c>
       <c r="AD18" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6047.6527411200004</v>
       </c>
       <c r="AE18" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7257.1832893440005</v>
       </c>
       <c r="AF18" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8708.619947212801</v>
       </c>
       <c r="AG18" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10450.343936655361</v>
       </c>
       <c r="AH18" s="4">
@@ -2150,175 +2144,175 @@
         <v>10554.847376021915</v>
       </c>
       <c r="AI18" s="4">
-        <f t="shared" ref="AI18:BY18" si="1">AH18*(1+$AC$43)</f>
+        <f t="shared" ref="AI18:BY18" si="2">AH18*(1+$AC$43)</f>
         <v>10660.395849782135</v>
       </c>
       <c r="AJ18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10766.999808279956</v>
       </c>
       <c r="AK18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10874.669806362755</v>
       </c>
       <c r="AL18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10983.416504426383</v>
       </c>
       <c r="AM18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11093.250669470646</v>
       </c>
       <c r="AN18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11204.183176165352</v>
       </c>
       <c r="AO18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11316.225007927005</v>
       </c>
       <c r="AP18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11429.387258006276</v>
       </c>
       <c r="AQ18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11543.681130586339</v>
       </c>
       <c r="AR18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11659.117941892202</v>
       </c>
       <c r="AS18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11775.709121311123</v>
       </c>
       <c r="AT18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11893.466212524234</v>
       </c>
       <c r="AU18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12012.400874649476</v>
       </c>
       <c r="AV18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12132.524883395972</v>
       </c>
       <c r="AW18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12253.850132229933</v>
       </c>
       <c r="AX18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12376.388633552231</v>
       </c>
       <c r="AY18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12500.152519887753</v>
       </c>
       <c r="AZ18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12625.154045086631</v>
       </c>
       <c r="BA18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12751.405585537497</v>
       </c>
       <c r="BB18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12878.919641392873</v>
       </c>
       <c r="BC18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13007.708837806802</v>
       </c>
       <c r="BD18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13137.78592618487</v>
       </c>
       <c r="BE18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13269.163785446719</v>
       </c>
       <c r="BF18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13401.855423301186</v>
       </c>
       <c r="BG18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13535.873977534198</v>
       </c>
       <c r="BH18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13671.23271730954</v>
       </c>
       <c r="BI18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13807.945044482636</v>
       </c>
       <c r="BJ18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13946.024494927462</v>
       </c>
       <c r="BK18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14085.484739876736</v>
       </c>
       <c r="BL18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14226.339587275503</v>
       </c>
       <c r="BM18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14368.602983148257</v>
       </c>
       <c r="BN18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14512.28901297974</v>
       </c>
       <c r="BO18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14657.411903109538</v>
       </c>
       <c r="BP18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14803.986022140634</v>
       </c>
       <c r="BQ18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14952.025882362041</v>
       </c>
       <c r="BR18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15101.546141185661</v>
       </c>
       <c r="BS18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15252.561602597518</v>
       </c>
       <c r="BT18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15405.087218623494</v>
       </c>
       <c r="BU18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15559.138090809729</v>
       </c>
       <c r="BV18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15714.729471717827</v>
       </c>
       <c r="BW18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15871.876766435005</v>
       </c>
       <c r="BX18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16030.595534099355</v>
       </c>
       <c r="BY18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16190.901489440348</v>
       </c>
     </row>
@@ -2360,7 +2354,7 @@
         <v>135.33100000000002</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" ref="N19:Q19" si="2">+N18-N20</f>
+        <f t="shared" ref="N19:Q19" si="3">+N18-N20</f>
         <v>142.584</v>
       </c>
       <c r="O19" s="10">
@@ -2370,11 +2364,11 @@
         <f>139.949+31.479</f>
         <v>171.428</v>
       </c>
-      <c r="Q19" s="34">
-        <f t="shared" si="2"/>
+      <c r="Q19" s="33">
+        <f t="shared" si="3"/>
         <v>164.32</v>
       </c>
-      <c r="R19" s="34">
+      <c r="R19" s="33">
         <f>+R18-R20</f>
         <v>171.07999999999998</v>
       </c>
@@ -2412,31 +2406,31 @@
         <v>31</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" ref="C20:I20" si="3">+C18-C19</f>
+        <f t="shared" ref="C20:I20" si="4">+C18-C19</f>
         <v>0</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>210.82000000000005</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>239.96899999999999</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>272.15200000000004</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>270.83099999999996</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>318.45400000000001</v>
       </c>
       <c r="I20" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>325.88</v>
       </c>
       <c r="J20" s="3">
@@ -2467,11 +2461,11 @@
         <f>P18-P19</f>
         <v>419.97400000000005</v>
       </c>
-      <c r="Q20" s="34">
+      <c r="Q20" s="33">
         <f>+Q18*0.74</f>
         <v>467.68</v>
       </c>
-      <c r="R20" s="34">
+      <c r="R20" s="33">
         <f>+R18*0.74</f>
         <v>486.92</v>
       </c>
@@ -2549,12 +2543,12 @@
       <c r="P21" s="10">
         <v>244.065</v>
       </c>
-      <c r="Q21" s="34">
-        <f t="shared" ref="Q21:Q23" si="4">+M21*1.05</f>
+      <c r="Q21" s="33">
+        <f t="shared" ref="Q21:Q23" si="5">+M21*1.05</f>
         <v>228.85170000000002</v>
       </c>
-      <c r="R21" s="34">
-        <f t="shared" ref="R21:R23" si="5">+N21*1.05</f>
+      <c r="R21" s="33">
+        <f t="shared" ref="R21:R23" si="6">+N21*1.05</f>
         <v>232.75539000000003</v>
       </c>
       <c r="U21" s="3">
@@ -2564,15 +2558,15 @@
         <v>699.20100000000002</v>
       </c>
       <c r="W21" s="3">
-        <f t="shared" ref="W21:W23" si="6">SUM(G21:J21)</f>
+        <f t="shared" ref="W21:W23" si="7">SUM(G21:J21)</f>
         <v>782.76</v>
       </c>
       <c r="X21" s="10">
-        <f t="shared" ref="X21:X23" si="7">SUM(K21:N21)</f>
+        <f t="shared" ref="X21:X23" si="8">SUM(K21:N21)</f>
         <v>880.60879999999997</v>
       </c>
       <c r="Y21" s="10">
-        <f t="shared" ref="Y21:Y23" si="8">SUM(O21:R21)</f>
+        <f t="shared" ref="Y21:Y23" si="9">SUM(O21:R21)</f>
         <v>926.59509000000003</v>
       </c>
       <c r="Z21" s="3">
@@ -2620,7 +2614,7 @@
         <v>151.41</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" ref="N22:N23" si="9">+J22*1.05</f>
+        <f t="shared" ref="N22:N23" si="10">+J22*1.05</f>
         <v>152.83064999999999</v>
       </c>
       <c r="O22" s="10">
@@ -2629,12 +2623,12 @@
       <c r="P22" s="10">
         <v>181.739</v>
       </c>
-      <c r="Q22" s="34">
-        <f t="shared" si="4"/>
+      <c r="Q22" s="33">
+        <f t="shared" si="5"/>
         <v>158.98050000000001</v>
       </c>
-      <c r="R22" s="34">
-        <f t="shared" si="5"/>
+      <c r="R22" s="33">
+        <f t="shared" si="6"/>
         <v>160.4721825</v>
       </c>
       <c r="U22" s="3">
@@ -2644,23 +2638,23 @@
         <v>421.69200000000001</v>
       </c>
       <c r="W22" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>515.94000000000005</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>599.26765</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>670.02068250000002</v>
       </c>
       <c r="Z22" s="3">
-        <f t="shared" ref="Z22:AA22" si="10">+Y22*1.05</f>
+        <f t="shared" ref="Z22:AA22" si="11">+Y22*1.05</f>
         <v>703.52171662500007</v>
       </c>
       <c r="AA22" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>738.69780245625009</v>
       </c>
     </row>
@@ -2700,7 +2694,7 @@
         <v>52.555999999999997</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>60.540900000000001</v>
       </c>
       <c r="O23" s="10">
@@ -2709,12 +2703,12 @@
       <c r="P23" s="10">
         <v>59.463999999999999</v>
       </c>
-      <c r="Q23" s="34">
-        <f t="shared" si="4"/>
+      <c r="Q23" s="33">
+        <f t="shared" si="5"/>
         <v>55.183799999999998</v>
       </c>
-      <c r="R23" s="34">
-        <f t="shared" si="5"/>
+      <c r="R23" s="33">
+        <f t="shared" si="6"/>
         <v>63.567945000000002</v>
       </c>
       <c r="U23" s="3">
@@ -2724,23 +2718,23 @@
         <v>160.49799999999999</v>
       </c>
       <c r="W23" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>193.55799999999999</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>224.43289999999999</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>232.990745</v>
       </c>
       <c r="Z23" s="3">
-        <f t="shared" ref="Z23:AA23" si="11">+Y23*1.05</f>
+        <f t="shared" ref="Z23:AA23" si="12">+Y23*1.05</f>
         <v>244.64028225000001</v>
       </c>
       <c r="AA23" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>256.87229636250004</v>
       </c>
     </row>
@@ -2749,95 +2743,95 @@
         <v>35</v>
       </c>
       <c r="C24" s="3">
-        <f t="shared" ref="C24:N24" si="12">SUM(C21:C23)</f>
+        <f t="shared" ref="C24:N24" si="13">SUM(C21:C23)</f>
         <v>0</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>330.226</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>322.89200000000005</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>345.101</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>339.37800000000004</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>367.45699999999999</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>371.096</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>414.327</v>
       </c>
       <c r="K24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>426.05</v>
       </c>
       <c r="L24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>421.29599999999999</v>
       </c>
       <c r="M24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>421.92</v>
       </c>
       <c r="N24" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>435.04335000000003</v>
       </c>
       <c r="O24" s="3">
-        <f t="shared" ref="O24:R24" si="13">SUM(O21:O23)</f>
+        <f t="shared" ref="O24:R24" si="14">SUM(O21:O23)</f>
         <v>444.52699999999999</v>
       </c>
       <c r="P24" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>485.26799999999997</v>
       </c>
-      <c r="Q24" s="36">
-        <f t="shared" si="13"/>
+      <c r="Q24" s="35">
+        <f t="shared" si="14"/>
         <v>443.01600000000008</v>
       </c>
-      <c r="R24" s="36">
-        <f t="shared" si="13"/>
+      <c r="R24" s="35">
+        <f t="shared" si="14"/>
         <v>456.79551750000007</v>
       </c>
       <c r="U24" s="3">
-        <f t="shared" ref="U24" si="14">SUM(U21:U23)</f>
+        <f t="shared" ref="U24" si="15">SUM(U21:U23)</f>
         <v>903.654</v>
       </c>
       <c r="V24" s="3">
-        <f t="shared" ref="V24:W24" si="15">SUM(V21:V23)</f>
+        <f t="shared" ref="V24:W24" si="16">SUM(V21:V23)</f>
         <v>1281.3910000000001</v>
       </c>
       <c r="W24" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1492.258</v>
       </c>
       <c r="X24" s="3">
-        <f t="shared" ref="X24:Y24" si="16">SUM(X21:X23)</f>
+        <f t="shared" ref="X24:Y24" si="17">SUM(X21:X23)</f>
         <v>1704.30935</v>
       </c>
       <c r="Y24" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1829.6065175000001</v>
       </c>
       <c r="Z24" s="3">
-        <f t="shared" ref="Z24:AA24" si="17">SUM(Z21:Z23)</f>
+        <f t="shared" ref="Z24:AA24" si="18">SUM(Z21:Z23)</f>
         <v>1921.0868433750002</v>
       </c>
       <c r="AA24" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2017.1411855437502</v>
       </c>
     </row>
@@ -2846,95 +2840,95 @@
         <v>36</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" ref="C25:N25" si="18">C20-C24</f>
+        <f t="shared" ref="C25:N25" si="19">C20-C24</f>
         <v>0</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-119.40599999999995</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-82.923000000000059</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-72.948999999999955</v>
       </c>
       <c r="G25" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-68.547000000000082</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-49.002999999999986</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-45.216000000000008</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-70.966000000000008</v>
       </c>
       <c r="K25" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-98.185999999999979</v>
       </c>
       <c r="L25" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-71.44</v>
       </c>
       <c r="M25" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-27.876000000000033</v>
       </c>
       <c r="N25" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-29.227350000000058</v>
       </c>
       <c r="O25" s="3">
-        <f t="shared" ref="O25:R25" si="19">O20-O24</f>
+        <f t="shared" ref="O25:R25" si="20">O20-O24</f>
         <v>-53.553999999999974</v>
       </c>
       <c r="P25" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-65.293999999999926</v>
       </c>
-      <c r="Q25" s="36">
-        <f t="shared" si="19"/>
+      <c r="Q25" s="35">
+        <f t="shared" si="20"/>
         <v>24.66399999999993</v>
       </c>
-      <c r="R25" s="36">
-        <f t="shared" si="19"/>
+      <c r="R25" s="35">
+        <f t="shared" si="20"/>
         <v>30.124482499999942</v>
       </c>
       <c r="U25" s="3">
-        <f t="shared" ref="U25" si="20">U20-U24</f>
+        <f t="shared" ref="U25" si="21">U20-U24</f>
         <v>-289.36400000000003</v>
       </c>
       <c r="V25" s="3">
-        <f t="shared" ref="V25:W25" si="21">V20-V24</f>
+        <f t="shared" ref="V25:W25" si="22">V20-V24</f>
         <v>-346.6550000000002</v>
       </c>
       <c r="W25" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-233.7320000000002</v>
       </c>
       <c r="X25" s="3">
-        <f t="shared" ref="X25:Y25" si="22">X20-X24</f>
+        <f t="shared" ref="X25:Y25" si="23">X20-X24</f>
         <v>-226.72934999999984</v>
       </c>
       <c r="Y25" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-64.059517499999856</v>
       </c>
       <c r="Z25" s="3">
-        <f t="shared" ref="Z25:AA25" si="23">Z20-Z24</f>
+        <f t="shared" ref="Z25:AA25" si="24">Z20-Z24</f>
         <v>266.28755662499998</v>
       </c>
       <c r="AA25" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>607.70809445625014</v>
       </c>
     </row>
@@ -2989,11 +2983,11 @@
         <f>23.637-1.473</f>
         <v>22.164000000000001</v>
       </c>
-      <c r="Q26" s="34">
+      <c r="Q26" s="33">
         <f>+P26</f>
         <v>22.164000000000001</v>
       </c>
-      <c r="R26" s="34">
+      <c r="R26" s="33">
         <f>+Q26</f>
         <v>22.164000000000001</v>
       </c>
@@ -3006,15 +3000,15 @@
         <v>13.401</v>
       </c>
       <c r="W26" s="3">
-        <f t="shared" ref="W26" si="24">SUM(G26:J26)</f>
+        <f t="shared" ref="W26" si="25">SUM(G26:J26)</f>
         <v>70.215999999999994</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" ref="X26" si="25">SUM(K26:N26)</f>
+        <f t="shared" ref="X26" si="26">SUM(K26:N26)</f>
         <v>82.515999999999991</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" ref="Y26:Y28" si="26">SUM(O26:R26)</f>
+        <f t="shared" ref="Y26:Y28" si="27">SUM(O26:R26)</f>
         <v>86.722000000000008</v>
       </c>
       <c r="Z26" s="3">
@@ -3031,35 +3025,35 @@
         <v>38</v>
       </c>
       <c r="C27" s="3">
-        <f t="shared" ref="C27:J27" si="27">+C25+C26</f>
+        <f t="shared" ref="C27:J27" si="28">+C25+C26</f>
         <v>0</v>
       </c>
       <c r="D27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-120.37899999999995</v>
       </c>
       <c r="E27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-79.806000000000054</v>
       </c>
       <c r="F27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-61.483999999999952</v>
       </c>
       <c r="G27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-51.759000000000086</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-34.008999999999986</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-25.662000000000006</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-52.086000000000013</v>
       </c>
       <c r="K27" s="3">
@@ -3079,47 +3073,47 @@
         <v>-8.4603500000000587</v>
       </c>
       <c r="O27" s="3">
-        <f t="shared" ref="O27:R27" si="28">+O25+O26</f>
+        <f t="shared" ref="O27:R27" si="29">+O25+O26</f>
         <v>-33.32399999999997</v>
       </c>
       <c r="P27" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-43.129999999999924</v>
       </c>
-      <c r="Q27" s="36">
-        <f t="shared" si="28"/>
+      <c r="Q27" s="35">
+        <f t="shared" si="29"/>
         <v>46.827999999999932</v>
       </c>
-      <c r="R27" s="36">
-        <f t="shared" si="28"/>
+      <c r="R27" s="35">
+        <f t="shared" si="29"/>
         <v>52.288482499999944</v>
       </c>
       <c r="U27" s="3">
-        <f t="shared" ref="U27:AA27" si="29">+U25+U26</f>
+        <f t="shared" ref="U27:AA27" si="30">+U25+U26</f>
         <v>-302.88900000000001</v>
       </c>
       <c r="V27" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-333.25400000000019</v>
       </c>
       <c r="W27" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-163.51600000000019</v>
       </c>
       <c r="X27" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-144.21334999999985</v>
       </c>
       <c r="Y27" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>22.662482500000152</v>
       </c>
       <c r="Z27" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>353.00955662499996</v>
       </c>
       <c r="AA27" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>694.43009445625012</v>
       </c>
     </row>
@@ -3167,10 +3161,10 @@
       <c r="P28" s="25">
         <v>3.9279999999999999</v>
       </c>
-      <c r="Q28" s="32">
+      <c r="Q28" s="31">
         <v>0</v>
       </c>
-      <c r="R28" s="32">
+      <c r="R28" s="31">
         <v>0</v>
       </c>
       <c r="U28" s="3">
@@ -3180,15 +3174,15 @@
         <v>12.144</v>
       </c>
       <c r="W28" s="3">
-        <f t="shared" ref="W28" si="30">SUM(G28:J28)</f>
+        <f t="shared" ref="W28" si="31">SUM(G28:J28)</f>
         <v>13.084000000000001</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" ref="X28" si="31">SUM(K28:N28)</f>
+        <f t="shared" ref="X28" si="32">SUM(K28:N28)</f>
         <v>9.1449999999999996</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8.23</v>
       </c>
       <c r="Z28" s="3">
@@ -3205,35 +3199,35 @@
         <v>8</v>
       </c>
       <c r="C29" s="3">
-        <f t="shared" ref="C29:J29" si="32">+C27-C28</f>
+        <f t="shared" ref="C29:J29" si="33">+C27-C28</f>
         <v>0</v>
       </c>
       <c r="D29" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-123.42799999999995</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-84.841000000000051</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-64.397999999999954</v>
       </c>
       <c r="G29" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-54.246000000000087</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-37.596999999999987</v>
       </c>
       <c r="I29" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-29.297000000000004</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-55.460000000000015</v>
       </c>
       <c r="K29" s="3">
@@ -3253,47 +3247,47 @@
         <v>-8.4603500000000587</v>
       </c>
       <c r="O29" s="3">
-        <f t="shared" ref="O29:R29" si="33">+O27-O28</f>
+        <f t="shared" ref="O29:R29" si="34">+O27-O28</f>
         <v>-37.625999999999969</v>
       </c>
       <c r="P29" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-47.057999999999922</v>
       </c>
-      <c r="Q29" s="36">
-        <f t="shared" si="33"/>
+      <c r="Q29" s="35">
+        <f t="shared" si="34"/>
         <v>46.827999999999932</v>
       </c>
-      <c r="R29" s="36">
-        <f t="shared" si="33"/>
+      <c r="R29" s="35">
+        <f t="shared" si="34"/>
         <v>52.288482499999944</v>
       </c>
       <c r="U29" s="3">
-        <f t="shared" ref="U29:AA29" si="34">+U27-U28</f>
+        <f t="shared" ref="U29:AA29" si="35">+U27-U28</f>
         <v>-306.86599999999999</v>
       </c>
       <c r="V29" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-345.3980000000002</v>
       </c>
       <c r="W29" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-176.60000000000019</v>
       </c>
       <c r="X29" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-153.35834999999986</v>
       </c>
       <c r="Y29" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>14.432482500000152</v>
       </c>
       <c r="Z29" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>317.70860096249999</v>
       </c>
       <c r="AA29" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>555.54407556500007</v>
       </c>
     </row>
@@ -3302,35 +3296,35 @@
         <v>40</v>
       </c>
       <c r="C30" s="7" t="e">
-        <f t="shared" ref="C30:J30" si="35">C29/C31</f>
+        <f t="shared" ref="C30:J30" si="36">C29/C31</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D30" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-1.8062335280774275</v>
       </c>
       <c r="E30" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-1.2310638914773968</v>
       </c>
       <c r="F30" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-0.92625357140093434</v>
       </c>
       <c r="G30" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-0.77298280464511981</v>
       </c>
       <c r="H30" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-0.53047574476307036</v>
       </c>
       <c r="I30" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-0.40940456377438567</v>
       </c>
       <c r="J30" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-0.76655837267370075</v>
       </c>
       <c r="K30" s="7">
@@ -3350,47 +3344,47 @@
         <v>-0.11429724698368815</v>
       </c>
       <c r="O30" s="7">
-        <f t="shared" ref="O30:R30" si="36">O29/O31</f>
+        <f t="shared" ref="O30:R30" si="37">O29/O31</f>
         <v>-0.46416997843915236</v>
       </c>
       <c r="P30" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.58040405535410244</v>
       </c>
-      <c r="Q30" s="37">
-        <f t="shared" si="36"/>
+      <c r="Q30" s="36">
+        <f t="shared" si="37"/>
         <v>0.57756728089000631</v>
       </c>
-      <c r="R30" s="37">
-        <f t="shared" si="36"/>
+      <c r="R30" s="36">
+        <f t="shared" si="37"/>
         <v>0.64491579096672269</v>
       </c>
       <c r="U30" s="7">
-        <f t="shared" ref="U30:AA30" si="37">U29/U31</f>
+        <f t="shared" ref="U30:AA30" si="38">U29/U31</f>
         <v>-4.7529676115582671</v>
       </c>
       <c r="V30" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-5.0328824418661222</v>
       </c>
       <c r="W30" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-2.478935809701309</v>
       </c>
       <c r="X30" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-1.8933129629629613</v>
       </c>
       <c r="Y30" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.17817879629629818</v>
       </c>
       <c r="Z30" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>3.9223284069444442</v>
       </c>
       <c r="AA30" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>6.8585688341358031</v>
       </c>
     </row>
@@ -3439,12 +3433,12 @@
       <c r="P31" s="10">
         <v>81.078000000000003</v>
       </c>
-      <c r="Q31" s="34">
-        <f t="shared" ref="Q31:R31" si="38">+P31</f>
+      <c r="Q31" s="33">
+        <f t="shared" ref="Q31:R31" si="39">+P31</f>
         <v>81.078000000000003</v>
       </c>
-      <c r="R31" s="34">
-        <f t="shared" si="38"/>
+      <c r="R31" s="33">
+        <f t="shared" si="39"/>
         <v>81.078000000000003</v>
       </c>
       <c r="U31" s="3">
@@ -3479,71 +3473,71 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5">
-        <f t="shared" ref="H33:R33" si="39">H18/D18-1</f>
+        <f t="shared" ref="H33:R33" si="40">H18/D18-1</f>
         <v>0.39188825245014303</v>
       </c>
       <c r="I33" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.29769409000032976</v>
       </c>
       <c r="J33" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.26760805065981752</v>
       </c>
       <c r="K33" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.22341968067774531</v>
       </c>
       <c r="L33" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.12817166952578041</v>
       </c>
       <c r="M33" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.22275013974287305</v>
       </c>
       <c r="N33" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.19737468395334501</v>
       </c>
       <c r="O33" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.21851203277691589</v>
       </c>
       <c r="P33" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.23696060940078523</v>
       </c>
-      <c r="Q33" s="38">
-        <f t="shared" si="39"/>
+      <c r="Q33" s="37">
+        <f t="shared" si="40"/>
         <v>0.19386068476977569</v>
       </c>
-      <c r="R33" s="38">
-        <f t="shared" si="39"/>
+      <c r="R33" s="37">
+        <f t="shared" si="40"/>
         <v>0.19985412107950395</v>
       </c>
       <c r="V33" s="19">
-        <f t="shared" ref="V33:AA33" si="40">+V18/U18-1</f>
+        <f t="shared" ref="V33:AA33" si="41">+V18/U18-1</f>
         <v>0.46951985735572488</v>
       </c>
       <c r="W33" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.31071539827419703</v>
       </c>
       <c r="X33" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.19217580871426287</v>
       </c>
       <c r="Y33" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.21130457101988842</v>
       </c>
       <c r="Z33" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AA33" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.19999999999999996</v>
       </c>
     </row>
@@ -3552,91 +3546,91 @@
         <v>90</v>
       </c>
       <c r="D34" s="19">
-        <f t="shared" ref="D34:F34" si="41">+D20/D18</f>
+        <f t="shared" ref="D34:F34" si="42">+D20/D18</f>
         <v>0.69241178170734918</v>
       </c>
       <c r="E34" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.71928625596110563</v>
       </c>
       <c r="F34" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.75323266318306625</v>
       </c>
       <c r="G34" s="19">
-        <f t="shared" ref="G34:L34" si="42">+G20/G18</f>
+        <f t="shared" ref="G34:L34" si="43">+G20/G18</f>
         <v>0.73539426523297491</v>
       </c>
       <c r="H34" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.75144115849557924</v>
       </c>
       <c r="I34" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.75271747917715703</v>
       </c>
       <c r="J34" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.74969323278064282</v>
       </c>
       <c r="K34" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.72767949289885281</v>
       </c>
       <c r="L34" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.73174945462227237</v>
       </c>
       <c r="M34" s="19">
-        <f t="shared" ref="M34:R34" si="43">+M20/M18</f>
+        <f t="shared" ref="M34:R34" si="44">+M20/M18</f>
         <v>0.74435702479338839</v>
       </c>
       <c r="N34" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.74</v>
       </c>
       <c r="O34" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.71213666682452548</v>
       </c>
       <c r="P34" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.71013287070385289</v>
       </c>
-      <c r="Q34" s="39">
-        <f t="shared" si="43"/>
+      <c r="Q34" s="38">
+        <f t="shared" si="44"/>
         <v>0.74</v>
       </c>
-      <c r="R34" s="39">
-        <f t="shared" si="43"/>
+      <c r="R34" s="38">
+        <f t="shared" si="44"/>
         <v>0.74</v>
       </c>
       <c r="U34" s="19">
-        <f t="shared" ref="U34:AA34" si="44">+U20/U18</f>
+        <f t="shared" ref="U34:AA34" si="45">+U20/U18</f>
         <v>0.703024324144924</v>
       </c>
       <c r="V34" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.7279648609077598</v>
       </c>
       <c r="W34" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.74778239714416594</v>
       </c>
       <c r="X34" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.73641689655086484</v>
       </c>
       <c r="Y34" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.7264381900053325</v>
       </c>
       <c r="Z34" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.75</v>
       </c>
       <c r="AA34" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.75</v>
       </c>
     </row>
@@ -3652,47 +3646,47 @@
         <v>0.16547387398895153</v>
       </c>
       <c r="H35" s="19">
-        <f t="shared" ref="H35:R35" si="45">-(H30-G30)/G30</f>
+        <f t="shared" ref="H35:R35" si="46">-(H30-G30)/G30</f>
         <v>0.31372891922658697</v>
       </c>
       <c r="I35" s="19">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.22823132289066195</v>
       </c>
       <c r="J35" s="19">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-0.8723737850077683</v>
       </c>
       <c r="K35" s="19">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-0.44041583847270299</v>
       </c>
       <c r="L35" s="19">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.32849299077262684</v>
       </c>
       <c r="M35" s="19">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.8218749648825493</v>
       </c>
       <c r="N35" s="19">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.13457958265138814</v>
       </c>
       <c r="O35" s="19">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-3.0610775035149889</v>
       </c>
       <c r="P35" s="19">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-0.25041274169821626</v>
       </c>
-      <c r="Q35" s="39">
-        <f t="shared" si="45"/>
+      <c r="Q35" s="38">
+        <f t="shared" si="46"/>
         <v>1.9951124144672536</v>
       </c>
-      <c r="R35" s="39">
-        <f t="shared" si="45"/>
+      <c r="R35" s="38">
+        <f t="shared" si="46"/>
         <v>-0.11660721149739513</v>
       </c>
       <c r="U35" s="19"/>
@@ -3717,8 +3711,8 @@
       <c r="N36" s="19"/>
       <c r="O36" s="19"/>
       <c r="P36" s="19"/>
-      <c r="Q36" s="39"/>
-      <c r="R36" s="39"/>
+      <c r="Q36" s="38"/>
+      <c r="R36" s="38"/>
       <c r="U36" s="19"/>
       <c r="V36" s="19"/>
       <c r="W36" s="19"/>
@@ -3744,69 +3738,69 @@
       <c r="N37" s="19"/>
       <c r="O37" s="19"/>
       <c r="P37" s="19"/>
-      <c r="Q37" s="39"/>
-      <c r="R37" s="39"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="28">
+      <c r="Q37" s="38"/>
+      <c r="R37" s="38"/>
+      <c r="U37" s="27"/>
+      <c r="V37" s="27"/>
+      <c r="W37" s="27">
         <v>121.5</v>
       </c>
-      <c r="X37" s="28">
+      <c r="X37" s="27">
         <v>150.19999999999999</v>
       </c>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="27"/>
-      <c r="AC37" s="27"/>
-      <c r="AD37" s="27"/>
-      <c r="AE37" s="27"/>
-      <c r="AF37" s="27"/>
-      <c r="AG37" s="27"/>
-      <c r="AH37" s="27"/>
-      <c r="AI37" s="27"/>
-      <c r="AJ37" s="27"/>
-      <c r="AK37" s="27"/>
-      <c r="AL37" s="27"/>
-      <c r="AM37" s="27"/>
-      <c r="AN37" s="27"/>
-      <c r="AO37" s="27"/>
-      <c r="AP37" s="27"/>
-      <c r="AQ37" s="27"/>
-      <c r="AR37" s="27"/>
-      <c r="AS37" s="27"/>
-      <c r="AT37" s="27"/>
-      <c r="AU37" s="27"/>
-      <c r="AV37" s="27"/>
-      <c r="AW37" s="27"/>
-      <c r="AX37" s="27"/>
-      <c r="AY37" s="27"/>
-      <c r="AZ37" s="27"/>
-      <c r="BA37" s="27"/>
-      <c r="BB37" s="27"/>
-      <c r="BC37" s="27"/>
-      <c r="BD37" s="27"/>
-      <c r="BE37" s="27"/>
-      <c r="BF37" s="27"/>
-      <c r="BG37" s="27"/>
-      <c r="BH37" s="27"/>
-      <c r="BI37" s="27"/>
-      <c r="BJ37" s="27"/>
-      <c r="BK37" s="27"/>
-      <c r="BL37" s="27"/>
-      <c r="BM37" s="27"/>
-      <c r="BN37" s="27"/>
-      <c r="BO37" s="27"/>
-      <c r="BP37" s="27"/>
-      <c r="BQ37" s="27"/>
-      <c r="BR37" s="27"/>
-      <c r="BS37" s="27"/>
-      <c r="BT37" s="27"/>
-      <c r="BU37" s="27"/>
-      <c r="BV37" s="27"/>
-      <c r="BW37" s="27"/>
-      <c r="BX37" s="27"/>
-      <c r="BY37" s="27"/>
+      <c r="Y37" s="27"/>
+      <c r="Z37" s="27"/>
+      <c r="AA37" s="27"/>
+      <c r="AB37" s="26"/>
+      <c r="AC37" s="26"/>
+      <c r="AD37" s="26"/>
+      <c r="AE37" s="26"/>
+      <c r="AF37" s="26"/>
+      <c r="AG37" s="26"/>
+      <c r="AH37" s="26"/>
+      <c r="AI37" s="26"/>
+      <c r="AJ37" s="26"/>
+      <c r="AK37" s="26"/>
+      <c r="AL37" s="26"/>
+      <c r="AM37" s="26"/>
+      <c r="AN37" s="26"/>
+      <c r="AO37" s="26"/>
+      <c r="AP37" s="26"/>
+      <c r="AQ37" s="26"/>
+      <c r="AR37" s="26"/>
+      <c r="AS37" s="26"/>
+      <c r="AT37" s="26"/>
+      <c r="AU37" s="26"/>
+      <c r="AV37" s="26"/>
+      <c r="AW37" s="26"/>
+      <c r="AX37" s="26"/>
+      <c r="AY37" s="26"/>
+      <c r="AZ37" s="26"/>
+      <c r="BA37" s="26"/>
+      <c r="BB37" s="26"/>
+      <c r="BC37" s="26"/>
+      <c r="BD37" s="26"/>
+      <c r="BE37" s="26"/>
+      <c r="BF37" s="26"/>
+      <c r="BG37" s="26"/>
+      <c r="BH37" s="26"/>
+      <c r="BI37" s="26"/>
+      <c r="BJ37" s="26"/>
+      <c r="BK37" s="26"/>
+      <c r="BL37" s="26"/>
+      <c r="BM37" s="26"/>
+      <c r="BN37" s="26"/>
+      <c r="BO37" s="26"/>
+      <c r="BP37" s="26"/>
+      <c r="BQ37" s="26"/>
+      <c r="BR37" s="26"/>
+      <c r="BS37" s="26"/>
+      <c r="BT37" s="26"/>
+      <c r="BU37" s="26"/>
+      <c r="BV37" s="26"/>
+      <c r="BW37" s="26"/>
+      <c r="BX37" s="26"/>
+      <c r="BY37" s="26"/>
     </row>
     <row r="38" spans="2:77" x14ac:dyDescent="0.2">
       <c r="D38" s="19"/>
@@ -3822,8 +3816,8 @@
       <c r="N38" s="19"/>
       <c r="O38" s="19"/>
       <c r="P38" s="19"/>
-      <c r="Q38" s="39"/>
-      <c r="R38" s="39"/>
+      <c r="Q38" s="38"/>
+      <c r="R38" s="38"/>
       <c r="U38" s="19"/>
       <c r="V38" s="19"/>
       <c r="W38" s="19"/>
@@ -3870,8 +3864,8 @@
       <c r="AB41" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="AF41" s="41"/>
-      <c r="AG41" s="41" t="s">
+      <c r="AF41" s="40"/>
+      <c r="AG41" s="40" t="s">
         <v>119</v>
       </c>
     </row>
@@ -3903,10 +3897,10 @@
       <c r="AC42" s="5">
         <v>0.2</v>
       </c>
-      <c r="AF42" s="41" t="s">
+      <c r="AF42" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="AG42" s="41">
+      <c r="AG42" s="40">
         <v>15</v>
       </c>
     </row>
@@ -3938,10 +3932,10 @@
       <c r="AC43" s="5">
         <v>0.01</v>
       </c>
-      <c r="AF43" s="41" t="s">
+      <c r="AF43" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="AG43" s="41">
+      <c r="AG43" s="40">
         <v>10</v>
       </c>
     </row>
@@ -3973,10 +3967,10 @@
       <c r="AC44" s="5">
         <v>0.11</v>
       </c>
-      <c r="AF44" s="41" t="s">
+      <c r="AF44" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="AG44" s="41">
+      <c r="AG44" s="40">
         <v>5.65</v>
       </c>
     </row>
@@ -4102,7 +4096,7 @@
       </c>
       <c r="AC48" s="23">
         <f>(AC47-Main!J2)/Main!J2</f>
-        <v>0.92046795430531836</v>
+        <v>0.68904254577138857</v>
       </c>
     </row>
     <row r="49" spans="2:33" x14ac:dyDescent="0.2">
@@ -4161,11 +4155,11 @@
     </row>
     <row r="51" spans="2:33" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L51" s="3"/>
-      <c r="AB51" s="26" t="s">
+      <c r="AB51" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="AC51" s="26"/>
-      <c r="AD51" s="26"/>
+      <c r="AC51" s="41"/>
+      <c r="AD51" s="41"/>
       <c r="AE51" s="24"/>
       <c r="AF51" s="24"/>
       <c r="AG51" s="24"/>
@@ -4453,15 +4447,15 @@
         <v>-9.7760000000000336</v>
       </c>
       <c r="U63" s="10">
-        <f t="shared" ref="U63:W63" si="46">+U29</f>
+        <f t="shared" ref="U63:W63" si="47">+U29</f>
         <v>-306.86599999999999</v>
       </c>
       <c r="V63" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-345.3980000000002</v>
       </c>
       <c r="W63" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-176.60000000000019</v>
       </c>
       <c r="X63" s="10">
@@ -4984,15 +4978,15 @@
         <v>35.457000000000001</v>
       </c>
       <c r="U91" s="3">
-        <f t="shared" ref="U91:W91" si="47">+U71+U73</f>
+        <f t="shared" ref="U91:W91" si="48">+U71+U73</f>
         <v>-1.0920000000000236</v>
       </c>
       <c r="V91" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>-20.21399999999997</v>
       </c>
       <c r="W91" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>113.405</v>
       </c>
     </row>
